--- a/storage/app/data-assessees.xlsx
+++ b/storage/app/data-assessees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Telkom University\Magang Bio Farma\Project\Website\lsp-dashboard\storage\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40E5765-6548-42D4-A99A-17BA062D5113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1B3FB3-255D-46EF-BE0B-4A3E52EE13E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9B447020-AA2D-40C1-B0DE-AE97807CA751}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2327" uniqueCount="802">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3101" uniqueCount="804">
   <si>
     <t>Nama Asesi</t>
   </si>
@@ -2445,6 +2445,12 @@
   </si>
   <si>
     <t>Muhamad Mahadir</t>
+  </si>
+  <si>
+    <t>Internal</t>
+  </si>
+  <si>
+    <t>Eksternal</t>
   </si>
 </sst>
 </file>
@@ -2983,9 +2989,8 @@
       <c r="B2" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C2" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C2" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D2" s="16"/>
       <c r="E2" s="5" t="s">
@@ -2999,9 +3004,8 @@
       <c r="B3" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C3" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C3" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D3" s="16"/>
       <c r="E3" s="5" t="s">
@@ -3015,9 +3019,8 @@
       <c r="B4" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C4" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C4" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D4" s="16"/>
       <c r="E4" s="5" t="s">
@@ -3031,9 +3034,8 @@
       <c r="B5" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C5" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C5" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="5" t="s">
@@ -3047,9 +3049,8 @@
       <c r="B6" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C6" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C6" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D6" s="16"/>
       <c r="E6" s="5" t="s">
@@ -3063,9 +3064,8 @@
       <c r="B7" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C7" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C7" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="5" t="s">
@@ -3079,9 +3079,8 @@
       <c r="B8" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C8" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C8" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="5" t="s">
@@ -3095,9 +3094,8 @@
       <c r="B9" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C9" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C9" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="5" t="s">
@@ -3111,9 +3109,8 @@
       <c r="B10" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C10" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C10" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D10" s="16"/>
       <c r="E10" s="5" t="s">
@@ -3127,9 +3124,8 @@
       <c r="B11" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C11" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C11" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D11" s="16"/>
       <c r="E11" s="5" t="s">
@@ -3143,9 +3139,8 @@
       <c r="B12" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C12" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C12" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D12" s="16"/>
       <c r="E12" s="5" t="s">
@@ -3159,9 +3154,8 @@
       <c r="B13" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C13" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C13" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D13" s="16"/>
       <c r="E13" s="5" t="s">
@@ -3175,9 +3169,8 @@
       <c r="B14" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C14" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C14" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D14" s="16"/>
       <c r="E14" s="5" t="s">
@@ -3191,9 +3184,8 @@
       <c r="B15" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C15" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C15" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D15" s="16"/>
       <c r="E15" s="5" t="s">
@@ -3207,9 +3199,8 @@
       <c r="B16" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C16" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C16" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D16" s="16"/>
       <c r="E16" s="5" t="s">
@@ -3223,9 +3214,8 @@
       <c r="B17" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C17" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C17" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D17" s="16"/>
       <c r="E17" s="5" t="s">
@@ -3239,9 +3229,8 @@
       <c r="B18" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C18" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C18" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D18" s="16"/>
       <c r="E18" s="5" t="s">
@@ -3255,9 +3244,8 @@
       <c r="B19" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C19" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C19" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D19" s="16"/>
       <c r="E19" s="5" t="s">
@@ -3271,9 +3259,8 @@
       <c r="B20" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C20" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C20" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D20" s="16"/>
       <c r="E20" s="5" t="s">
@@ -3287,9 +3274,8 @@
       <c r="B21" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C21" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C21" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D21" s="16"/>
       <c r="E21" s="5" t="s">
@@ -3303,9 +3289,8 @@
       <c r="B22" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C22" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C22" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D22" s="16"/>
       <c r="E22" s="5" t="s">
@@ -3319,9 +3304,8 @@
       <c r="B23" s="4" t="s">
         <v>624</v>
       </c>
-      <c r="C23" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C23" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D23" s="16"/>
       <c r="E23" s="4" t="s">
@@ -3335,9 +3319,8 @@
       <c r="B24" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="C24" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C24" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D24" s="16"/>
       <c r="E24" s="5" t="s">
@@ -3351,9 +3334,8 @@
       <c r="B25" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="C25" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C25" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D25" s="16"/>
       <c r="E25" s="5" t="s">
@@ -3367,9 +3349,8 @@
       <c r="B26" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="C26" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C26" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D26" s="16"/>
       <c r="E26" s="5" t="s">
@@ -3383,9 +3364,8 @@
       <c r="B27" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="C27" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C27" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D27" s="16"/>
       <c r="E27" s="5" t="s">
@@ -3399,9 +3379,8 @@
       <c r="B28" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="C28" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C28" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="5" t="s">
@@ -3415,9 +3394,8 @@
       <c r="B29" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="C29" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C29" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D29" s="16"/>
       <c r="E29" s="5" t="s">
@@ -3431,9 +3409,8 @@
       <c r="B30" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="C30" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C30" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D30" s="16"/>
       <c r="E30" s="5" t="s">
@@ -3447,9 +3424,8 @@
       <c r="B31" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="C31" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C31" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D31" s="16"/>
       <c r="E31" s="5" t="s">
@@ -3463,9 +3439,8 @@
       <c r="B32" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="C32" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C32" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D32" s="16"/>
       <c r="E32" s="5" t="s">
@@ -3479,9 +3454,8 @@
       <c r="B33" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="C33" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C33" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D33" s="16"/>
       <c r="E33" s="5" t="s">
@@ -3495,9 +3469,8 @@
       <c r="B34" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="C34" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C34" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D34" s="16"/>
       <c r="E34" s="5" t="s">
@@ -3511,9 +3484,8 @@
       <c r="B35" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="C35" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C35" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D35" s="16"/>
       <c r="E35" s="5" t="s">
@@ -3527,9 +3499,8 @@
       <c r="B36" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="C36" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C36" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D36" s="16"/>
       <c r="E36" s="5" t="s">
@@ -3543,9 +3514,8 @@
       <c r="B37" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="C37" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C37" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D37" s="16"/>
       <c r="E37" s="5" t="s">
@@ -3559,9 +3529,8 @@
       <c r="B38" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="C38" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C38" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D38" s="16"/>
       <c r="E38" s="5" t="s">
@@ -3575,9 +3544,8 @@
       <c r="B39" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="C39" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C39" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D39" s="16"/>
       <c r="E39" s="18" t="s">
@@ -3591,9 +3559,8 @@
       <c r="B40" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="C40" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C40" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D40" s="16"/>
       <c r="E40" s="18" t="s">
@@ -3607,9 +3574,8 @@
       <c r="B41" s="6" t="s">
         <v>624</v>
       </c>
-      <c r="C41" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C41" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D41" s="16"/>
       <c r="E41" s="18" t="s">
@@ -3623,9 +3589,8 @@
       <c r="B42" s="6" t="s">
         <v>624</v>
       </c>
-      <c r="C42" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C42" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D42" s="16"/>
       <c r="E42" s="18" t="s">
@@ -3639,9 +3604,8 @@
       <c r="B43" s="6" t="s">
         <v>624</v>
       </c>
-      <c r="C43" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C43" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D43" s="16"/>
       <c r="E43" s="18" t="s">
@@ -3655,9 +3619,8 @@
       <c r="B44" s="6" t="s">
         <v>624</v>
       </c>
-      <c r="C44" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C44" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D44" s="16"/>
       <c r="E44" s="18" t="s">
@@ -3671,9 +3634,8 @@
       <c r="B45" s="6" t="s">
         <v>624</v>
       </c>
-      <c r="C45" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C45" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D45" s="16"/>
       <c r="E45" s="18" t="s">
@@ -3687,9 +3649,8 @@
       <c r="B46" s="6" t="s">
         <v>624</v>
       </c>
-      <c r="C46" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C46" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D46" s="16"/>
       <c r="E46" s="18" t="s">
@@ -3703,9 +3664,8 @@
       <c r="B47" s="6" t="s">
         <v>624</v>
       </c>
-      <c r="C47" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C47" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D47" s="16"/>
       <c r="E47" s="18" t="s">
@@ -3719,9 +3679,8 @@
       <c r="B48" s="6" t="s">
         <v>624</v>
       </c>
-      <c r="C48" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C48" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D48" s="16"/>
       <c r="E48" s="18" t="s">
@@ -3735,9 +3694,8 @@
       <c r="B49" s="6" t="s">
         <v>718</v>
       </c>
-      <c r="C49" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C49" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D49" s="16"/>
       <c r="E49" s="18" t="s">
@@ -3751,9 +3709,8 @@
       <c r="B50" s="6" t="s">
         <v>718</v>
       </c>
-      <c r="C50" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C50" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D50" s="16"/>
       <c r="E50" s="18" t="s">
@@ -3767,9 +3724,8 @@
       <c r="B51" s="7" t="s">
         <v>624</v>
       </c>
-      <c r="C51" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C51" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D51" s="16"/>
       <c r="E51" s="18" t="s">
@@ -3783,9 +3739,8 @@
       <c r="B52" s="7" t="s">
         <v>624</v>
       </c>
-      <c r="C52" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C52" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D52" s="16"/>
       <c r="E52" s="18" t="s">
@@ -3799,9 +3754,8 @@
       <c r="B53" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="C53" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C53" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D53" s="16"/>
       <c r="E53" s="18" t="s">
@@ -3815,9 +3769,8 @@
       <c r="B54" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="C54" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C54" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D54" s="16"/>
       <c r="E54" s="18" t="s">
@@ -3831,9 +3784,8 @@
       <c r="B55" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="C55" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C55" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D55" s="16"/>
       <c r="E55" s="18" t="s">
@@ -3847,9 +3799,8 @@
       <c r="B56" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="C56" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C56" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D56" s="16"/>
       <c r="E56" s="18" t="s">
@@ -3863,9 +3814,8 @@
       <c r="B57" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="C57" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C57" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D57" s="16"/>
       <c r="E57" s="18" t="s">
@@ -3879,9 +3829,8 @@
       <c r="B58" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="C58" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C58" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D58" s="16"/>
       <c r="E58" s="18" t="s">
@@ -3895,9 +3844,8 @@
       <c r="B59" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="C59" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C59" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D59" s="16"/>
       <c r="E59" s="18" t="s">
@@ -3911,9 +3859,8 @@
       <c r="B60" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="C60" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C60" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D60" s="16"/>
       <c r="E60" s="18" t="s">
@@ -3927,9 +3874,8 @@
       <c r="B61" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="C61" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C61" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D61" s="16"/>
       <c r="E61" s="18" t="s">
@@ -3943,9 +3889,8 @@
       <c r="B62" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="C62" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C62" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D62" s="16"/>
       <c r="E62" s="18" t="s">
@@ -3959,9 +3904,8 @@
       <c r="B63" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="C63" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C63" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D63" s="16"/>
       <c r="E63" s="18" t="s">
@@ -3975,9 +3919,8 @@
       <c r="B64" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="C64" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C64" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D64" s="16"/>
       <c r="E64" s="18" t="s">
@@ -3991,9 +3934,8 @@
       <c r="B65" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="C65" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C65" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D65" s="16"/>
       <c r="E65" s="18" t="s">
@@ -4007,9 +3949,8 @@
       <c r="B66" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="C66" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C66" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D66" s="16"/>
       <c r="E66" s="18" t="s">
@@ -4023,9 +3964,8 @@
       <c r="B67" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="C67" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C67" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D67" s="16"/>
       <c r="E67" s="18" t="s">
@@ -4039,9 +3979,8 @@
       <c r="B68" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="C68" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C68" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D68" s="16"/>
       <c r="E68" s="18" t="s">
@@ -4055,9 +3994,8 @@
       <c r="B69" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="C69" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C69" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D69" s="16"/>
       <c r="E69" s="18" t="s">
@@ -4071,9 +4009,8 @@
       <c r="B70" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="C70" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C70" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D70" s="16"/>
       <c r="E70" s="18" t="s">
@@ -4087,9 +4024,8 @@
       <c r="B71" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="C71" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C71" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D71" s="16"/>
       <c r="E71" s="18" t="s">
@@ -4103,9 +4039,8 @@
       <c r="B72" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C72" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C72" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D72" s="16"/>
       <c r="E72" s="12" t="s">
@@ -4119,9 +4054,8 @@
       <c r="B73" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C73" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C73" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D73" s="16"/>
       <c r="E73" s="12" t="s">
@@ -4135,9 +4069,8 @@
       <c r="B74" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C74" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C74" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D74" s="16"/>
       <c r="E74" s="12" t="s">
@@ -4151,9 +4084,8 @@
       <c r="B75" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C75" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C75" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D75" s="16"/>
       <c r="E75" s="12" t="s">
@@ -4167,9 +4099,8 @@
       <c r="B76" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C76" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C76" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D76" s="16"/>
       <c r="E76" s="12" t="s">
@@ -4183,9 +4114,8 @@
       <c r="B77" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C77" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C77" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D77" s="16"/>
       <c r="E77" s="12" t="s">
@@ -4199,9 +4129,8 @@
       <c r="B78" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C78" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C78" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D78" s="16"/>
       <c r="E78" s="12" t="s">
@@ -4215,9 +4144,8 @@
       <c r="B79" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C79" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C79" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D79" s="16"/>
       <c r="E79" s="12" t="s">
@@ -4231,9 +4159,8 @@
       <c r="B80" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C80" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C80" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D80" s="16"/>
       <c r="E80" s="12" t="s">
@@ -4247,9 +4174,8 @@
       <c r="B81" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C81" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C81" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D81" s="16"/>
       <c r="E81" s="12" t="s">
@@ -4263,9 +4189,8 @@
       <c r="B82" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C82" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C82" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D82" s="16"/>
       <c r="E82" s="12" t="s">
@@ -4279,9 +4204,8 @@
       <c r="B83" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C83" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C83" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D83" s="16"/>
       <c r="E83" s="12" t="s">
@@ -4295,9 +4219,8 @@
       <c r="B84" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C84" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C84" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D84" s="16"/>
       <c r="E84" s="12" t="s">
@@ -4311,9 +4234,8 @@
       <c r="B85" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C85" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C85" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D85" s="16"/>
       <c r="E85" s="12" t="s">
@@ -4327,9 +4249,8 @@
       <c r="B86" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C86" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C86" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D86" s="16"/>
       <c r="E86" s="12" t="s">
@@ -4343,9 +4264,8 @@
       <c r="B87" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C87" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C87" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D87" s="16"/>
       <c r="E87" s="12" t="s">
@@ -4359,9 +4279,8 @@
       <c r="B88" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C88" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C88" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D88" s="16"/>
       <c r="E88" s="12" t="s">
@@ -4375,9 +4294,8 @@
       <c r="B89" s="10" t="s">
         <v>718</v>
       </c>
-      <c r="C89" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C89" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D89" s="16"/>
       <c r="E89" s="12" t="s">
@@ -4391,9 +4309,8 @@
       <c r="B90" s="10" t="s">
         <v>718</v>
       </c>
-      <c r="C90" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C90" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D90" s="16"/>
       <c r="E90" s="12" t="s">
@@ -4407,9 +4324,8 @@
       <c r="B91" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C91" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C91" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D91" s="16"/>
       <c r="E91" s="12" t="s">
@@ -4423,9 +4339,8 @@
       <c r="B92" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C92" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C92" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D92" s="16"/>
       <c r="E92" s="12" t="s">
@@ -4439,9 +4354,8 @@
       <c r="B93" s="10" t="s">
         <v>718</v>
       </c>
-      <c r="C93" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C93" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D93" s="16"/>
       <c r="E93" s="12" t="s">
@@ -4455,9 +4369,8 @@
       <c r="B94" s="10" t="s">
         <v>718</v>
       </c>
-      <c r="C94" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C94" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D94" s="16"/>
       <c r="E94" s="12" t="s">
@@ -4471,9 +4384,8 @@
       <c r="B95" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C95" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C95" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D95" s="16"/>
       <c r="E95" s="12" t="s">
@@ -4487,9 +4399,8 @@
       <c r="B96" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C96" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C96" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D96" s="16"/>
       <c r="E96" s="9" t="s">
@@ -4503,9 +4414,8 @@
       <c r="B97" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C97" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C97" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D97" s="16"/>
       <c r="E97" s="9" t="s">
@@ -4519,9 +4429,8 @@
       <c r="B98" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C98" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C98" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D98" s="16"/>
       <c r="E98" s="9" t="s">
@@ -4535,9 +4444,8 @@
       <c r="B99" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C99" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C99" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D99" s="16"/>
       <c r="E99" s="9" t="s">
@@ -4551,9 +4459,8 @@
       <c r="B100" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C100" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C100" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D100" s="16"/>
       <c r="E100" s="9" t="s">
@@ -4567,9 +4474,8 @@
       <c r="B101" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C101" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C101" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D101" s="16"/>
       <c r="E101" s="9" t="s">
@@ -4583,9 +4489,8 @@
       <c r="B102" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C102" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C102" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D102" s="16"/>
       <c r="E102" s="9" t="s">
@@ -4599,9 +4504,8 @@
       <c r="B103" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C103" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C103" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D103" s="16"/>
       <c r="E103" s="9" t="s">
@@ -4615,9 +4519,8 @@
       <c r="B104" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C104" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C104" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D104" s="16"/>
       <c r="E104" s="9" t="s">
@@ -4631,9 +4534,8 @@
       <c r="B105" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C105" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C105" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D105" s="16"/>
       <c r="E105" s="9" t="s">
@@ -4647,9 +4549,8 @@
       <c r="B106" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C106" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C106" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D106" s="16"/>
       <c r="E106" s="9" t="s">
@@ -4663,9 +4564,8 @@
       <c r="B107" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C107" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C107" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D107" s="16"/>
       <c r="E107" s="9" t="s">
@@ -4679,9 +4579,8 @@
       <c r="B108" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C108" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C108" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D108" s="16"/>
       <c r="E108" s="9" t="s">
@@ -4695,9 +4594,8 @@
       <c r="B109" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C109" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C109" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D109" s="16"/>
       <c r="E109" s="9" t="s">
@@ -4711,9 +4609,8 @@
       <c r="B110" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C110" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C110" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D110" s="16"/>
       <c r="E110" s="9" t="s">
@@ -4727,9 +4624,8 @@
       <c r="B111" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C111" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C111" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D111" s="16"/>
       <c r="E111" s="9" t="s">
@@ -4743,9 +4639,8 @@
       <c r="B112" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="C112" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C112" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D112" s="16"/>
       <c r="E112" s="9" t="s">
@@ -4759,9 +4654,8 @@
       <c r="B113" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C113" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C113" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D113" s="16"/>
       <c r="E113" s="9" t="s">
@@ -4775,9 +4669,8 @@
       <c r="B114" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C114" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C114" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D114" s="16"/>
       <c r="E114" s="9" t="s">
@@ -4791,9 +4684,8 @@
       <c r="B115" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C115" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C115" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D115" s="16"/>
       <c r="E115" s="9" t="s">
@@ -4807,9 +4699,8 @@
       <c r="B116" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C116" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C116" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D116" s="16"/>
       <c r="E116" s="9" t="s">
@@ -4823,9 +4714,8 @@
       <c r="B117" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C117" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C117" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D117" s="16"/>
       <c r="E117" s="9" t="s">
@@ -4839,9 +4729,8 @@
       <c r="B118" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C118" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C118" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D118" s="16"/>
       <c r="E118" s="9" t="s">
@@ -4855,9 +4744,8 @@
       <c r="B119" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C119" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C119" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D119" s="16"/>
       <c r="E119" s="9" t="s">
@@ -4871,9 +4759,8 @@
       <c r="B120" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C120" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C120" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D120" s="16"/>
       <c r="E120" s="9" t="s">
@@ -4887,9 +4774,8 @@
       <c r="B121" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C121" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C121" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D121" s="16"/>
       <c r="E121" s="9" t="s">
@@ -4903,9 +4789,8 @@
       <c r="B122" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C122" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C122" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D122" s="16"/>
       <c r="E122" s="9" t="s">
@@ -4919,9 +4804,8 @@
       <c r="B123" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C123" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C123" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D123" s="16"/>
       <c r="E123" s="9" t="s">
@@ -4935,9 +4819,8 @@
       <c r="B124" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C124" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C124" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D124" s="16"/>
       <c r="E124" s="9" t="s">
@@ -4951,9 +4834,8 @@
       <c r="B125" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="C125" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C125" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D125" s="16"/>
       <c r="E125" s="9" t="s">
@@ -4967,9 +4849,8 @@
       <c r="B126" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C126" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C126" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D126" s="16"/>
       <c r="E126" s="9" t="s">
@@ -4983,9 +4864,8 @@
       <c r="B127" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C127" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C127" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D127" s="16"/>
       <c r="E127" s="9" t="s">
@@ -4999,9 +4879,8 @@
       <c r="B128" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C128" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C128" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D128" s="16"/>
       <c r="E128" s="9" t="s">
@@ -5015,9 +4894,8 @@
       <c r="B129" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C129" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C129" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D129" s="16"/>
       <c r="E129" s="12" t="s">
@@ -5031,9 +4909,8 @@
       <c r="B130" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C130" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C130" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D130" s="16"/>
       <c r="E130" s="12" t="s">
@@ -5047,9 +4924,8 @@
       <c r="B131" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C131" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C131" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D131" s="16"/>
       <c r="E131" s="12" t="s">
@@ -5063,9 +4939,8 @@
       <c r="B132" s="12" t="s">
         <v>719</v>
       </c>
-      <c r="C132" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C132" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D132" s="16"/>
       <c r="E132" s="12" t="s">
@@ -5079,9 +4954,8 @@
       <c r="B133" s="12" t="s">
         <v>719</v>
       </c>
-      <c r="C133" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C133" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D133" s="16"/>
       <c r="E133" s="12" t="s">
@@ -5095,9 +4969,8 @@
       <c r="B134" s="12" t="s">
         <v>719</v>
       </c>
-      <c r="C134" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C134" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D134" s="16"/>
       <c r="E134" s="12" t="s">
@@ -5111,9 +4984,8 @@
       <c r="B135" s="12" t="s">
         <v>719</v>
       </c>
-      <c r="C135" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C135" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D135" s="16"/>
       <c r="E135" s="12" t="s">
@@ -5127,9 +4999,8 @@
       <c r="B136" s="12" t="s">
         <v>719</v>
       </c>
-      <c r="C136" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C136" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D136" s="16"/>
       <c r="E136" s="12" t="s">
@@ -5143,9 +5014,8 @@
       <c r="B137" s="12" t="s">
         <v>719</v>
       </c>
-      <c r="C137" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C137" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D137" s="16"/>
       <c r="E137" s="12" t="s">
@@ -5159,9 +5029,8 @@
       <c r="B138" s="12" t="s">
         <v>719</v>
       </c>
-      <c r="C138" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C138" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D138" s="16"/>
       <c r="E138" s="12" t="s">
@@ -5175,9 +5044,8 @@
       <c r="B139" s="12" t="s">
         <v>719</v>
       </c>
-      <c r="C139" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C139" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D139" s="16"/>
       <c r="E139" s="12" t="s">
@@ -5191,9 +5059,8 @@
       <c r="B140" s="12" t="s">
         <v>719</v>
       </c>
-      <c r="C140" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C140" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D140" s="16"/>
       <c r="E140" s="12" t="s">
@@ -5207,9 +5074,8 @@
       <c r="B141" s="12" t="s">
         <v>719</v>
       </c>
-      <c r="C141" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C141" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D141" s="16"/>
       <c r="E141" s="12" t="s">
@@ -5223,9 +5089,8 @@
       <c r="B142" s="12" t="s">
         <v>624</v>
       </c>
-      <c r="C142" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C142" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D142" s="16"/>
       <c r="E142" s="12" t="s">
@@ -5239,9 +5104,8 @@
       <c r="B143" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C143" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C143" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D143" s="16"/>
       <c r="E143" s="12" t="s">
@@ -5255,9 +5119,8 @@
       <c r="B144" s="12" t="s">
         <v>717</v>
       </c>
-      <c r="C144" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C144" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D144" s="16"/>
       <c r="E144" s="12" t="s">
@@ -5271,9 +5134,8 @@
       <c r="B145" s="12" t="s">
         <v>719</v>
       </c>
-      <c r="C145" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C145" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D145" s="16"/>
       <c r="E145" s="12" t="s">
@@ -5287,9 +5149,8 @@
       <c r="B146" s="12" t="s">
         <v>719</v>
       </c>
-      <c r="C146" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C146" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D146" s="16"/>
       <c r="E146" s="12" t="s">
@@ -5303,9 +5164,8 @@
       <c r="B147" s="12" t="s">
         <v>719</v>
       </c>
-      <c r="C147" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C147" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D147" s="16"/>
       <c r="E147" s="12" t="s">
@@ -5319,9 +5179,8 @@
       <c r="B148" s="12" t="s">
         <v>719</v>
       </c>
-      <c r="C148" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C148" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D148" s="16"/>
       <c r="E148" s="12" t="s">
@@ -5335,9 +5194,8 @@
       <c r="B149" s="12" t="s">
         <v>624</v>
       </c>
-      <c r="C149" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C149" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D149" s="16"/>
       <c r="E149" s="12" t="s">
@@ -5351,9 +5209,8 @@
       <c r="B150" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C150" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C150" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D150" s="16"/>
       <c r="E150" s="12" t="s">
@@ -5367,9 +5224,8 @@
       <c r="B151" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C151" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C151" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D151" s="16"/>
       <c r="E151" s="9" t="s">
@@ -5383,9 +5239,8 @@
       <c r="B152" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C152" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C152" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D152" s="16"/>
       <c r="E152" s="9" t="s">
@@ -5399,9 +5254,8 @@
       <c r="B153" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C153" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C153" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D153" s="16"/>
       <c r="E153" s="9" t="s">
@@ -5415,9 +5269,8 @@
       <c r="B154" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C154" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C154" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D154" s="16"/>
       <c r="E154" s="9" t="s">
@@ -5431,9 +5284,8 @@
       <c r="B155" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C155" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C155" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D155" s="16"/>
       <c r="E155" s="9" t="s">
@@ -5447,9 +5299,8 @@
       <c r="B156" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C156" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C156" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D156" s="16"/>
       <c r="E156" s="9" t="s">
@@ -5463,9 +5314,8 @@
       <c r="B157" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C157" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C157" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D157" s="16"/>
       <c r="E157" s="9" t="s">
@@ -5479,9 +5329,8 @@
       <c r="B158" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C158" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C158" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D158" s="16"/>
       <c r="E158" s="9" t="s">
@@ -5495,9 +5344,8 @@
       <c r="B159" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C159" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C159" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D159" s="16"/>
       <c r="E159" s="9" t="s">
@@ -5511,9 +5359,8 @@
       <c r="B160" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C160" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C160" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D160" s="16"/>
       <c r="E160" s="9" t="s">
@@ -5527,9 +5374,8 @@
       <c r="B161" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C161" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C161" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D161" s="16"/>
       <c r="E161" s="9" t="s">
@@ -5543,9 +5389,8 @@
       <c r="B162" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C162" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C162" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D162" s="16"/>
       <c r="E162" s="9" t="s">
@@ -5559,9 +5404,8 @@
       <c r="B163" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C163" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C163" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D163" s="16"/>
       <c r="E163" s="9" t="s">
@@ -5575,9 +5419,8 @@
       <c r="B164" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C164" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C164" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D164" s="16"/>
       <c r="E164" s="9" t="s">
@@ -5591,9 +5434,8 @@
       <c r="B165" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C165" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C165" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D165" s="16"/>
       <c r="E165" s="9" t="s">
@@ -5607,9 +5449,8 @@
       <c r="B166" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C166" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C166" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D166" s="16"/>
       <c r="E166" s="9" t="s">
@@ -5623,9 +5464,8 @@
       <c r="B167" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C167" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C167" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D167" s="16"/>
       <c r="E167" s="9" t="s">
@@ -5639,9 +5479,8 @@
       <c r="B168" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C168" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C168" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D168" s="16"/>
       <c r="E168" s="9" t="s">
@@ -5655,9 +5494,8 @@
       <c r="B169" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C169" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C169" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D169" s="16"/>
       <c r="E169" s="9" t="s">
@@ -5671,9 +5509,8 @@
       <c r="B170" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C170" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C170" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D170" s="16"/>
       <c r="E170" s="9" t="s">
@@ -5687,9 +5524,8 @@
       <c r="B171" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C171" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C171" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D171" s="16"/>
       <c r="E171" s="9" t="s">
@@ -5703,9 +5539,8 @@
       <c r="B172" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C172" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C172" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D172" s="16"/>
       <c r="E172" s="9" t="s">
@@ -5719,9 +5554,8 @@
       <c r="B173" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C173" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C173" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D173" s="16"/>
       <c r="E173" s="9" t="s">
@@ -5735,9 +5569,8 @@
       <c r="B174" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C174" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C174" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D174" s="16"/>
       <c r="E174" s="9" t="s">
@@ -5751,9 +5584,8 @@
       <c r="B175" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C175" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C175" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D175" s="16"/>
       <c r="E175" s="9" t="s">
@@ -5767,9 +5599,8 @@
       <c r="B176" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C176" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C176" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D176" s="16"/>
       <c r="E176" s="9" t="s">
@@ -5783,9 +5614,8 @@
       <c r="B177" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="C177" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C177" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D177" s="16"/>
       <c r="E177" s="9" t="s">
@@ -5799,9 +5629,8 @@
       <c r="B178" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C178" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C178" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D178" s="16"/>
       <c r="E178" s="9" t="s">
@@ -5815,9 +5644,8 @@
       <c r="B179" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C179" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C179" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D179" s="16"/>
       <c r="E179" s="12" t="s">
@@ -5831,9 +5659,8 @@
       <c r="B180" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C180" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C180" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D180" s="16"/>
       <c r="E180" s="12" t="s">
@@ -5847,9 +5674,8 @@
       <c r="B181" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C181" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C181" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D181" s="16"/>
       <c r="E181" s="12" t="s">
@@ -5863,9 +5689,8 @@
       <c r="B182" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C182" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C182" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D182" s="16"/>
       <c r="E182" s="12" t="s">
@@ -5879,9 +5704,8 @@
       <c r="B183" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C183" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C183" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D183" s="16"/>
       <c r="E183" s="12" t="s">
@@ -5895,9 +5719,8 @@
       <c r="B184" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C184" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C184" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D184" s="16"/>
       <c r="E184" s="12" t="s">
@@ -5911,9 +5734,8 @@
       <c r="B185" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C185" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C185" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D185" s="16"/>
       <c r="E185" s="12" t="s">
@@ -5927,9 +5749,8 @@
       <c r="B186" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C186" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C186" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D186" s="16"/>
       <c r="E186" s="12" t="s">
@@ -5943,9 +5764,8 @@
       <c r="B187" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C187" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C187" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D187" s="16"/>
       <c r="E187" s="12" t="s">
@@ -5959,9 +5779,8 @@
       <c r="B188" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C188" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C188" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D188" s="16"/>
       <c r="E188" s="12" t="s">
@@ -5975,9 +5794,8 @@
       <c r="B189" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C189" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C189" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D189" s="16"/>
       <c r="E189" s="12" t="s">
@@ -5991,9 +5809,8 @@
       <c r="B190" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C190" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C190" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D190" s="16"/>
       <c r="E190" s="12" t="s">
@@ -6007,9 +5824,8 @@
       <c r="B191" s="10" t="s">
         <v>718</v>
       </c>
-      <c r="C191" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C191" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D191" s="16"/>
       <c r="E191" s="12" t="s">
@@ -6023,9 +5839,8 @@
       <c r="B192" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C192" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C192" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D192" s="16"/>
       <c r="E192" s="12" t="s">
@@ -6039,9 +5854,8 @@
       <c r="B193" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C193" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C193" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D193" s="16"/>
       <c r="E193" s="12" t="s">
@@ -6055,9 +5869,8 @@
       <c r="B194" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C194" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C194" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D194" s="16"/>
       <c r="E194" s="12" t="s">
@@ -6071,9 +5884,8 @@
       <c r="B195" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C195" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C195" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D195" s="16"/>
       <c r="E195" s="12" t="s">
@@ -6087,9 +5899,8 @@
       <c r="B196" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C196" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C196" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D196" s="16"/>
       <c r="E196" s="12" t="s">
@@ -6103,9 +5914,8 @@
       <c r="B197" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C197" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C197" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D197" s="16"/>
       <c r="E197" s="12" t="s">
@@ -6119,9 +5929,8 @@
       <c r="B198" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C198" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C198" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D198" s="16"/>
       <c r="E198" s="12" t="s">
@@ -6135,9 +5944,8 @@
       <c r="B199" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C199" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C199" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D199" s="16"/>
       <c r="E199" s="12" t="s">
@@ -6151,9 +5959,8 @@
       <c r="B200" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C200" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C200" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D200" s="16"/>
       <c r="E200" s="12" t="s">
@@ -6167,9 +5974,8 @@
       <c r="B201" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C201" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C201" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D201" s="16"/>
       <c r="E201" s="12" t="s">
@@ -6183,9 +5989,8 @@
       <c r="B202" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C202" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C202" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D202" s="16"/>
       <c r="E202" s="12" t="s">
@@ -6199,9 +6004,8 @@
       <c r="B203" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C203" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C203" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D203" s="16"/>
       <c r="E203" s="12" t="s">
@@ -6215,9 +6019,8 @@
       <c r="B204" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="C204" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C204" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D204" s="16"/>
       <c r="E204" s="12" t="s">
@@ -6231,9 +6034,8 @@
       <c r="B205" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C205" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C205" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D205" s="16"/>
       <c r="E205" s="12" t="s">
@@ -6247,9 +6049,8 @@
       <c r="B206" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C206" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C206" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D206" s="16"/>
       <c r="E206" s="12" t="s">
@@ -6263,9 +6064,8 @@
       <c r="B207" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="C207" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C207" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D207" s="16"/>
       <c r="E207" s="12" t="s">
@@ -6279,9 +6079,8 @@
       <c r="B208" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="C208" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C208" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D208" s="16"/>
       <c r="E208" s="12" t="s">
@@ -6295,9 +6094,8 @@
       <c r="B209" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="C209" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C209" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D209" s="16"/>
       <c r="E209" s="12" t="s">
@@ -6311,9 +6109,8 @@
       <c r="B210" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="C210" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C210" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D210" s="16"/>
       <c r="E210" s="12" t="s">
@@ -6327,9 +6124,8 @@
       <c r="B211" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C211" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C211" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D211" s="16"/>
       <c r="E211" s="12" t="s">
@@ -6343,9 +6139,8 @@
       <c r="B212" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C212" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C212" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D212" s="16"/>
       <c r="E212" s="12" t="s">
@@ -6359,9 +6154,8 @@
       <c r="B213" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C213" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C213" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D213" s="16"/>
       <c r="E213" s="9" t="s">
@@ -6375,9 +6169,8 @@
       <c r="B214" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C214" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C214" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D214" s="16"/>
       <c r="E214" s="9" t="s">
@@ -6391,9 +6184,8 @@
       <c r="B215" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C215" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C215" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D215" s="16"/>
       <c r="E215" s="9" t="s">
@@ -6407,9 +6199,8 @@
       <c r="B216" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C216" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C216" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D216" s="16"/>
       <c r="E216" s="9" t="s">
@@ -6423,9 +6214,8 @@
       <c r="B217" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C217" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C217" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D217" s="16"/>
       <c r="E217" s="9" t="s">
@@ -6439,9 +6229,8 @@
       <c r="B218" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C218" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C218" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D218" s="16"/>
       <c r="E218" s="9" t="s">
@@ -6455,9 +6244,8 @@
       <c r="B219" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C219" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C219" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D219" s="16"/>
       <c r="E219" s="9" t="s">
@@ -6471,9 +6259,8 @@
       <c r="B220" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C220" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C220" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D220" s="16"/>
       <c r="E220" s="9" t="s">
@@ -6487,9 +6274,8 @@
       <c r="B221" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C221" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C221" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D221" s="16"/>
       <c r="E221" s="9" t="s">
@@ -6503,9 +6289,8 @@
       <c r="B222" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C222" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C222" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D222" s="16"/>
       <c r="E222" s="9" t="s">
@@ -6519,9 +6304,8 @@
       <c r="B223" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C223" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C223" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D223" s="16"/>
       <c r="E223" s="9" t="s">
@@ -6535,9 +6319,8 @@
       <c r="B224" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C224" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C224" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D224" s="16"/>
       <c r="E224" s="9" t="s">
@@ -6551,9 +6334,8 @@
       <c r="B225" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C225" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C225" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D225" s="16"/>
       <c r="E225" s="9" t="s">
@@ -6567,9 +6349,8 @@
       <c r="B226" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C226" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C226" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D226" s="16"/>
       <c r="E226" s="9" t="s">
@@ -6583,9 +6364,8 @@
       <c r="B227" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C227" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C227" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D227" s="16"/>
       <c r="E227" s="9" t="s">
@@ -6599,9 +6379,8 @@
       <c r="B228" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C228" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C228" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D228" s="16"/>
       <c r="E228" s="9" t="s">
@@ -6615,9 +6394,8 @@
       <c r="B229" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C229" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C229" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D229" s="16"/>
       <c r="E229" s="9" t="s">
@@ -6631,9 +6409,8 @@
       <c r="B230" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C230" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C230" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D230" s="16"/>
       <c r="E230" s="9" t="s">
@@ -6647,9 +6424,8 @@
       <c r="B231" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C231" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C231" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D231" s="16"/>
       <c r="E231" s="9" t="s">
@@ -6663,9 +6439,8 @@
       <c r="B232" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C232" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C232" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D232" s="16"/>
       <c r="E232" s="9" t="s">
@@ -6679,9 +6454,8 @@
       <c r="B233" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C233" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C233" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D233" s="16"/>
       <c r="E233" s="9" t="s">
@@ -6695,9 +6469,8 @@
       <c r="B234" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C234" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C234" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D234" s="16"/>
       <c r="E234" s="9" t="s">
@@ -6711,9 +6484,8 @@
       <c r="B235" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C235" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C235" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D235" s="16"/>
       <c r="E235" s="9" t="s">
@@ -6727,9 +6499,8 @@
       <c r="B236" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C236" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C236" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D236" s="16"/>
       <c r="E236" s="9" t="s">
@@ -6743,9 +6514,8 @@
       <c r="B237" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C237" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C237" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D237" s="16"/>
       <c r="E237" s="9" t="s">
@@ -6759,9 +6529,8 @@
       <c r="B238" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C238" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C238" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D238" s="16"/>
       <c r="E238" s="9" t="s">
@@ -6775,9 +6544,8 @@
       <c r="B239" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C239" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C239" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D239" s="16"/>
       <c r="E239" s="9" t="s">
@@ -6791,9 +6559,8 @@
       <c r="B240" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C240" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C240" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D240" s="16"/>
       <c r="E240" s="9" t="s">
@@ -6807,9 +6574,8 @@
       <c r="B241" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C241" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C241" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D241" s="16"/>
       <c r="E241" s="9" t="s">
@@ -6823,9 +6589,8 @@
       <c r="B242" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C242" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C242" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D242" s="16"/>
       <c r="E242" s="9" t="s">
@@ -6839,9 +6604,8 @@
       <c r="B243" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C243" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C243" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D243" s="16"/>
       <c r="E243" s="9" t="s">
@@ -6855,9 +6619,8 @@
       <c r="B244" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C244" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C244" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D244" s="16"/>
       <c r="E244" s="9" t="s">
@@ -6871,9 +6634,8 @@
       <c r="B245" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C245" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C245" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D245" s="16"/>
       <c r="E245" s="9" t="s">
@@ -6887,9 +6649,8 @@
       <c r="B246" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C246" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C246" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D246" s="16"/>
       <c r="E246" s="9" t="s">
@@ -6903,9 +6664,8 @@
       <c r="B247" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C247" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C247" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D247" s="16"/>
       <c r="E247" s="9" t="s">
@@ -6919,9 +6679,8 @@
       <c r="B248" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C248" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C248" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D248" s="16"/>
       <c r="E248" s="9" t="s">
@@ -6935,9 +6694,8 @@
       <c r="B249" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C249" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C249" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D249" s="16"/>
       <c r="E249" s="9" t="s">
@@ -6951,9 +6709,8 @@
       <c r="B250" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C250" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C250" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D250" s="16"/>
       <c r="E250" s="9" t="s">
@@ -6967,9 +6724,8 @@
       <c r="B251" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C251" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C251" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D251" s="16"/>
       <c r="E251" s="9" t="s">
@@ -6983,9 +6739,8 @@
       <c r="B252" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C252" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C252" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D252" s="16"/>
       <c r="E252" s="9" t="s">
@@ -6999,9 +6754,8 @@
       <c r="B253" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C253" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C253" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D253" s="16"/>
       <c r="E253" s="12" t="s">
@@ -7015,9 +6769,8 @@
       <c r="B254" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="C254" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C254" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D254" s="16"/>
       <c r="E254" s="12" t="s">
@@ -7031,9 +6784,8 @@
       <c r="B255" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="C255" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C255" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D255" s="16"/>
       <c r="E255" s="12" t="s">
@@ -7047,9 +6799,8 @@
       <c r="B256" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="C256" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C256" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D256" s="16"/>
       <c r="E256" s="12" t="s">
@@ -7063,9 +6814,8 @@
       <c r="B257" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="C257" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C257" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D257" s="16"/>
       <c r="E257" s="12" t="s">
@@ -7079,9 +6829,8 @@
       <c r="B258" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="C258" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C258" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D258" s="16"/>
       <c r="E258" s="12" t="s">
@@ -7095,9 +6844,8 @@
       <c r="B259" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="C259" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C259" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D259" s="16"/>
       <c r="E259" s="12" t="s">
@@ -7111,9 +6859,8 @@
       <c r="B260" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="C260" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C260" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D260" s="16"/>
       <c r="E260" s="12" t="s">
@@ -7127,9 +6874,8 @@
       <c r="B261" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="C261" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C261" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D261" s="16"/>
       <c r="E261" s="12" t="s">
@@ -7143,9 +6889,8 @@
       <c r="B262" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="C262" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C262" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D262" s="16"/>
       <c r="E262" s="12" t="s">
@@ -7159,9 +6904,8 @@
       <c r="B263" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="C263" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C263" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D263" s="16"/>
       <c r="E263" s="12" t="s">
@@ -7175,9 +6919,8 @@
       <c r="B264" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="C264" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C264" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D264" s="16"/>
       <c r="E264" s="12" t="s">
@@ -7191,9 +6934,8 @@
       <c r="B265" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C265" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C265" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D265" s="16"/>
       <c r="E265" s="12" t="s">
@@ -7207,9 +6949,8 @@
       <c r="B266" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="C266" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C266" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D266" s="16"/>
       <c r="E266" s="12" t="s">
@@ -7223,9 +6964,8 @@
       <c r="B267" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="C267" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C267" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D267" s="16"/>
       <c r="E267" s="12" t="s">
@@ -7239,9 +6979,8 @@
       <c r="B268" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="C268" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C268" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D268" s="16"/>
       <c r="E268" s="12" t="s">
@@ -7255,9 +6994,8 @@
       <c r="B269" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="C269" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C269" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D269" s="16"/>
       <c r="E269" s="12" t="s">
@@ -7271,9 +7009,8 @@
       <c r="B270" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C270" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C270" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D270" s="16"/>
       <c r="E270" s="12" t="s">
@@ -7287,9 +7024,8 @@
       <c r="B271" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C271" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C271" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D271" s="16"/>
       <c r="E271" s="12" t="s">
@@ -7303,9 +7039,8 @@
       <c r="B272" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C272" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C272" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D272" s="16"/>
       <c r="E272" s="12" t="s">
@@ -7319,9 +7054,8 @@
       <c r="B273" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C273" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C273" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D273" s="16"/>
       <c r="E273" s="9" t="s">
@@ -7335,9 +7069,8 @@
       <c r="B274" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C274" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C274" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D274" s="16"/>
       <c r="E274" s="9" t="s">
@@ -7351,9 +7084,8 @@
       <c r="B275" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C275" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C275" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D275" s="16"/>
       <c r="E275" s="9" t="s">
@@ -7367,9 +7099,8 @@
       <c r="B276" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C276" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C276" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D276" s="16"/>
       <c r="E276" s="9" t="s">
@@ -7383,9 +7114,8 @@
       <c r="B277" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C277" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C277" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D277" s="16"/>
       <c r="E277" s="9" t="s">
@@ -7399,9 +7129,8 @@
       <c r="B278" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C278" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C278" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D278" s="16"/>
       <c r="E278" s="9" t="s">
@@ -7415,9 +7144,8 @@
       <c r="B279" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C279" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C279" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D279" s="16"/>
       <c r="E279" s="9" t="s">
@@ -7431,9 +7159,8 @@
       <c r="B280" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C280" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C280" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D280" s="16"/>
       <c r="E280" s="9" t="s">
@@ -7447,9 +7174,8 @@
       <c r="B281" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C281" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C281" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D281" s="16"/>
       <c r="E281" s="9" t="s">
@@ -7463,9 +7189,8 @@
       <c r="B282" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C282" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C282" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D282" s="16"/>
       <c r="E282" s="9" t="s">
@@ -7479,9 +7204,8 @@
       <c r="B283" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C283" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C283" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D283" s="16"/>
       <c r="E283" s="9" t="s">
@@ -7495,9 +7219,8 @@
       <c r="B284" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C284" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C284" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D284" s="16"/>
       <c r="E284" s="9" t="s">
@@ -7511,9 +7234,8 @@
       <c r="B285" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C285" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C285" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D285" s="16"/>
       <c r="E285" s="9" t="s">
@@ -7527,9 +7249,8 @@
       <c r="B286" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C286" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C286" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D286" s="16"/>
       <c r="E286" s="9" t="s">
@@ -7543,9 +7264,8 @@
       <c r="B287" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C287" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C287" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D287" s="16"/>
       <c r="E287" s="9" t="s">
@@ -7559,9 +7279,8 @@
       <c r="B288" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C288" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C288" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D288" s="16"/>
       <c r="E288" s="9" t="s">
@@ -7575,9 +7294,8 @@
       <c r="B289" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C289" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C289" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D289" s="16"/>
       <c r="E289" s="9" t="s">
@@ -7591,9 +7309,8 @@
       <c r="B290" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C290" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C290" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D290" s="16"/>
       <c r="E290" s="9" t="s">
@@ -7607,9 +7324,8 @@
       <c r="B291" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C291" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C291" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D291" s="16"/>
       <c r="E291" s="9" t="s">
@@ -7623,9 +7339,8 @@
       <c r="B292" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C292" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C292" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D292" s="16"/>
       <c r="E292" s="9" t="s">
@@ -7639,9 +7354,8 @@
       <c r="B293" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C293" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C293" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D293" s="16"/>
       <c r="E293" s="9" t="s">
@@ -7655,9 +7369,8 @@
       <c r="B294" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C294" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C294" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D294" s="16"/>
       <c r="E294" s="9" t="s">
@@ -7671,9 +7384,8 @@
       <c r="B295" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C295" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C295" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D295" s="16"/>
       <c r="E295" s="9" t="s">
@@ -7687,9 +7399,8 @@
       <c r="B296" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C296" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C296" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D296" s="16"/>
       <c r="E296" s="9" t="s">
@@ -7703,9 +7414,8 @@
       <c r="B297" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C297" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C297" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D297" s="16"/>
       <c r="E297" s="9" t="s">
@@ -7719,9 +7429,8 @@
       <c r="B298" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C298" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C298" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D298" s="16"/>
       <c r="E298" s="9" t="s">
@@ -7735,9 +7444,8 @@
       <c r="B299" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C299" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C299" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D299" s="16"/>
       <c r="E299" s="9" t="s">
@@ -7751,9 +7459,8 @@
       <c r="B300" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C300" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C300" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D300" s="16"/>
       <c r="E300" s="9" t="s">
@@ -7767,9 +7474,8 @@
       <c r="B301" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C301" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C301" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D301" s="16"/>
       <c r="E301" s="9" t="s">
@@ -7783,9 +7489,8 @@
       <c r="B302" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C302" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C302" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D302" s="16"/>
       <c r="E302" s="9" t="s">
@@ -7799,9 +7504,8 @@
       <c r="B303" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C303" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C303" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D303" s="16"/>
       <c r="E303" s="12" t="s">
@@ -7815,9 +7519,8 @@
       <c r="B304" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C304" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C304" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D304" s="16"/>
       <c r="E304" s="12" t="s">
@@ -7831,9 +7534,8 @@
       <c r="B305" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C305" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C305" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D305" s="16"/>
       <c r="E305" s="12" t="s">
@@ -7847,9 +7549,8 @@
       <c r="B306" s="10" t="s">
         <v>718</v>
       </c>
-      <c r="C306" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C306" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D306" s="16"/>
       <c r="E306" s="12" t="s">
@@ -7863,9 +7564,8 @@
       <c r="B307" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C307" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C307" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D307" s="16"/>
       <c r="E307" s="12" t="s">
@@ -7879,9 +7579,8 @@
       <c r="B308" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C308" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C308" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D308" s="16"/>
       <c r="E308" s="9" t="s">
@@ -7895,9 +7594,8 @@
       <c r="B309" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C309" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C309" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D309" s="16"/>
       <c r="E309" s="9" t="s">
@@ -7911,9 +7609,8 @@
       <c r="B310" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C310" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C310" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D310" s="16"/>
       <c r="E310" s="9" t="s">
@@ -7927,9 +7624,8 @@
       <c r="B311" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C311" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C311" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D311" s="16"/>
       <c r="E311" s="9" t="s">
@@ -7943,9 +7639,8 @@
       <c r="B312" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C312" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C312" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D312" s="16"/>
       <c r="E312" s="9" t="s">
@@ -7959,9 +7654,8 @@
       <c r="B313" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C313" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C313" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D313" s="16"/>
       <c r="E313" s="9" t="s">
@@ -7975,9 +7669,8 @@
       <c r="B314" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C314" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C314" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D314" s="16"/>
       <c r="E314" s="9" t="s">
@@ -7991,9 +7684,8 @@
       <c r="B315" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C315" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C315" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D315" s="16"/>
       <c r="E315" s="9" t="s">
@@ -8007,9 +7699,8 @@
       <c r="B316" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C316" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C316" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D316" s="16"/>
       <c r="E316" s="9" t="s">
@@ -8023,9 +7714,8 @@
       <c r="B317" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C317" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C317" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D317" s="16"/>
       <c r="E317" s="9" t="s">
@@ -8039,9 +7729,8 @@
       <c r="B318" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C318" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C318" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D318" s="16"/>
       <c r="E318" s="9" t="s">
@@ -8055,9 +7744,8 @@
       <c r="B319" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C319" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C319" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D319" s="16"/>
       <c r="E319" s="9" t="s">
@@ -8071,9 +7759,8 @@
       <c r="B320" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C320" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C320" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D320" s="16"/>
       <c r="E320" s="9" t="s">
@@ -8087,9 +7774,8 @@
       <c r="B321" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C321" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C321" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D321" s="16"/>
       <c r="E321" s="9" t="s">
@@ -8103,9 +7789,8 @@
       <c r="B322" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C322" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C322" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D322" s="16"/>
       <c r="E322" s="9" t="s">
@@ -8119,9 +7804,8 @@
       <c r="B323" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C323" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C323" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D323" s="16"/>
       <c r="E323" s="9" t="s">
@@ -8135,9 +7819,8 @@
       <c r="B324" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C324" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C324" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D324" s="16"/>
       <c r="E324" s="9" t="s">
@@ -8151,9 +7834,8 @@
       <c r="B325" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C325" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C325" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D325" s="16"/>
       <c r="E325" s="9" t="s">
@@ -8167,9 +7849,8 @@
       <c r="B326" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C326" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C326" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D326" s="16"/>
       <c r="E326" s="9" t="s">
@@ -8183,9 +7864,8 @@
       <c r="B327" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C327" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C327" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D327" s="16"/>
       <c r="E327" s="9" t="s">
@@ -8199,9 +7879,8 @@
       <c r="B328" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C328" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C328" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D328" s="16"/>
       <c r="E328" s="9" t="s">
@@ -8215,9 +7894,8 @@
       <c r="B329" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C329" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C329" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D329" s="16"/>
       <c r="E329" s="9" t="s">
@@ -8231,9 +7909,8 @@
       <c r="B330" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C330" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C330" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D330" s="16"/>
       <c r="E330" s="9" t="s">
@@ -8247,9 +7924,8 @@
       <c r="B331" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C331" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C331" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D331" s="16"/>
       <c r="E331" s="9" t="s">
@@ -8263,9 +7939,8 @@
       <c r="B332" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C332" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C332" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D332" s="16"/>
       <c r="E332" s="9" t="s">
@@ -8279,9 +7954,8 @@
       <c r="B333" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C333" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C333" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D333" s="16"/>
       <c r="E333" s="9" t="s">
@@ -8295,9 +7969,8 @@
       <c r="B334" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C334" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C334" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D334" s="16"/>
       <c r="E334" s="9" t="s">
@@ -8311,9 +7984,8 @@
       <c r="B335" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C335" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C335" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D335" s="16"/>
       <c r="E335" s="9" t="s">
@@ -8327,9 +7999,8 @@
       <c r="B336" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C336" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C336" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D336" s="16"/>
       <c r="E336" s="9" t="s">
@@ -8343,9 +8014,8 @@
       <c r="B337" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C337" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C337" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D337" s="16"/>
       <c r="E337" s="9" t="s">
@@ -8359,9 +8029,8 @@
       <c r="B338" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C338" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C338" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D338" s="16"/>
       <c r="E338" s="9" t="s">
@@ -8375,9 +8044,8 @@
       <c r="B339" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C339" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C339" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D339" s="16"/>
       <c r="E339" s="9" t="s">
@@ -8391,9 +8059,8 @@
       <c r="B340" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C340" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C340" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D340" s="16"/>
       <c r="E340" s="9" t="s">
@@ -8407,9 +8074,8 @@
       <c r="B341" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C341" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C341" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D341" s="16"/>
       <c r="E341" s="9" t="s">
@@ -8423,9 +8089,8 @@
       <c r="B342" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C342" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C342" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D342" s="16"/>
       <c r="E342" s="9" t="s">
@@ -8439,9 +8104,8 @@
       <c r="B343" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C343" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C343" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D343" s="16"/>
       <c r="E343" s="9" t="s">
@@ -8455,9 +8119,8 @@
       <c r="B344" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C344" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C344" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D344" s="16"/>
       <c r="E344" s="9" t="s">
@@ -8471,9 +8134,8 @@
       <c r="B345" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C345" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C345" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D345" s="16"/>
       <c r="E345" s="12" t="s">
@@ -8487,9 +8149,8 @@
       <c r="B346" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C346" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C346" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D346" s="16"/>
       <c r="E346" s="12" t="s">
@@ -8503,9 +8164,8 @@
       <c r="B347" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C347" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C347" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D347" s="16"/>
       <c r="E347" s="12" t="s">
@@ -8519,9 +8179,8 @@
       <c r="B348" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C348" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C348" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D348" s="16"/>
       <c r="E348" s="12" t="s">
@@ -8535,9 +8194,8 @@
       <c r="B349" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C349" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C349" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D349" s="16"/>
       <c r="E349" s="12" t="s">
@@ -8551,9 +8209,8 @@
       <c r="B350" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C350" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C350" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D350" s="16"/>
       <c r="E350" s="12" t="s">
@@ -8567,9 +8224,8 @@
       <c r="B351" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C351" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C351" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D351" s="16"/>
       <c r="E351" s="12" t="s">
@@ -8583,9 +8239,8 @@
       <c r="B352" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C352" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C352" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D352" s="16"/>
       <c r="E352" s="12" t="s">
@@ -8599,9 +8254,8 @@
       <c r="B353" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C353" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C353" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D353" s="16"/>
       <c r="E353" s="12" t="s">
@@ -8615,9 +8269,8 @@
       <c r="B354" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C354" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C354" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D354" s="16"/>
       <c r="E354" s="12" t="s">
@@ -8631,9 +8284,8 @@
       <c r="B355" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C355" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C355" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D355" s="16"/>
       <c r="E355" s="12" t="s">
@@ -8647,9 +8299,8 @@
       <c r="B356" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C356" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C356" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D356" s="16"/>
       <c r="E356" s="12" t="s">
@@ -8663,9 +8314,8 @@
       <c r="B357" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C357" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C357" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D357" s="16"/>
       <c r="E357" s="12" t="s">
@@ -8679,9 +8329,8 @@
       <c r="B358" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C358" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C358" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D358" s="16"/>
       <c r="E358" s="12" t="s">
@@ -8695,9 +8344,8 @@
       <c r="B359" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C359" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C359" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D359" s="16"/>
       <c r="E359" s="12" t="s">
@@ -8711,9 +8359,8 @@
       <c r="B360" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C360" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C360" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D360" s="16"/>
       <c r="E360" s="12" t="s">
@@ -8727,9 +8374,8 @@
       <c r="B361" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C361" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C361" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D361" s="16"/>
       <c r="E361" s="12" t="s">
@@ -8743,9 +8389,8 @@
       <c r="B362" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C362" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C362" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D362" s="16"/>
       <c r="E362" s="12" t="s">
@@ -8759,9 +8404,8 @@
       <c r="B363" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C363" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C363" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D363" s="16"/>
       <c r="E363" s="12" t="s">
@@ -8775,9 +8419,8 @@
       <c r="B364" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C364" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C364" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D364" s="16"/>
       <c r="E364" s="12" t="s">
@@ -8791,9 +8434,8 @@
       <c r="B365" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C365" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C365" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D365" s="16"/>
       <c r="E365" s="12" t="s">
@@ -8807,9 +8449,8 @@
       <c r="B366" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C366" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C366" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D366" s="16"/>
       <c r="E366" s="12" t="s">
@@ -8823,9 +8464,8 @@
       <c r="B367" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C367" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C367" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D367" s="16"/>
       <c r="E367" s="12" t="s">
@@ -8839,9 +8479,8 @@
       <c r="B368" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C368" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C368" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D368" s="16"/>
       <c r="E368" s="12" t="s">
@@ -8855,9 +8494,8 @@
       <c r="B369" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C369" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C369" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D369" s="16"/>
       <c r="E369" s="12" t="s">
@@ -8871,9 +8509,8 @@
       <c r="B370" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C370" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C370" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D370" s="16"/>
       <c r="E370" s="12" t="s">
@@ -8887,9 +8524,8 @@
       <c r="B371" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C371" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C371" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D371" s="16"/>
       <c r="E371" s="12" t="s">
@@ -8903,9 +8539,8 @@
       <c r="B372" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C372" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C372" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D372" s="16"/>
       <c r="E372" s="12" t="s">
@@ -8919,9 +8554,8 @@
       <c r="B373" s="13" t="s">
         <v>717</v>
       </c>
-      <c r="C373" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C373" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D373" s="16"/>
       <c r="E373" s="12" t="s">
@@ -8935,9 +8569,8 @@
       <c r="B374" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C374" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C374" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D374" s="16"/>
       <c r="E374" s="12" t="s">
@@ -8951,9 +8584,8 @@
       <c r="B375" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C375" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C375" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D375" s="16"/>
       <c r="E375" s="12" t="s">
@@ -8967,9 +8599,8 @@
       <c r="B376" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C376" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C376" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D376" s="16"/>
       <c r="E376" s="12" t="s">
@@ -8983,9 +8614,8 @@
       <c r="B377" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C377" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C377" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D377" s="16"/>
       <c r="E377" s="12" t="s">
@@ -8999,9 +8629,8 @@
       <c r="B378" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C378" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C378" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D378" s="16"/>
       <c r="E378" s="12" t="s">
@@ -9015,9 +8644,8 @@
       <c r="B379" s="13" t="s">
         <v>717</v>
       </c>
-      <c r="C379" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C379" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D379" s="16"/>
       <c r="E379" s="12" t="s">
@@ -9031,9 +8659,8 @@
       <c r="B380" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C380" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C380" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D380" s="16"/>
       <c r="E380" s="12" t="s">
@@ -9047,9 +8674,8 @@
       <c r="B381" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C381" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C381" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D381" s="16"/>
       <c r="E381" s="12" t="s">
@@ -9063,9 +8689,8 @@
       <c r="B382" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C382" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C382" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D382" s="16"/>
       <c r="E382" s="12" t="s">
@@ -9079,9 +8704,8 @@
       <c r="B383" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C383" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C383" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D383" s="16"/>
       <c r="E383" s="12" t="s">
@@ -9095,9 +8719,8 @@
       <c r="B384" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C384" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C384" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D384" s="16"/>
       <c r="E384" s="12" t="s">
@@ -9111,9 +8734,8 @@
       <c r="B385" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C385" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C385" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D385" s="16"/>
       <c r="E385" s="12" t="s">
@@ -9127,9 +8749,8 @@
       <c r="B386" s="13" t="s">
         <v>717</v>
       </c>
-      <c r="C386" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C386" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D386" s="16"/>
       <c r="E386" s="12" t="s">
@@ -9143,9 +8764,8 @@
       <c r="B387" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C387" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C387" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D387" s="16"/>
       <c r="E387" s="12" t="s">
@@ -9159,9 +8779,8 @@
       <c r="B388" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C388" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C388" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D388" s="16"/>
       <c r="E388" s="12" t="s">
@@ -9175,9 +8794,8 @@
       <c r="B389" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C389" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C389" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D389" s="16"/>
       <c r="E389" s="12" t="s">
@@ -9191,9 +8809,8 @@
       <c r="B390" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C390" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C390" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D390" s="16"/>
       <c r="E390" s="12" t="s">
@@ -9207,9 +8824,8 @@
       <c r="B391" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C391" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C391" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D391" s="16"/>
       <c r="E391" s="12" t="s">
@@ -9223,9 +8839,8 @@
       <c r="B392" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C392" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C392" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D392" s="16"/>
       <c r="E392" s="12" t="s">
@@ -9239,9 +8854,8 @@
       <c r="B393" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C393" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C393" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D393" s="16"/>
       <c r="E393" s="12" t="s">
@@ -9255,9 +8869,8 @@
       <c r="B394" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C394" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C394" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D394" s="16"/>
       <c r="E394" s="12" t="s">
@@ -9271,9 +8884,8 @@
       <c r="B395" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C395" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C395" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D395" s="16"/>
       <c r="E395" s="12" t="s">
@@ -9287,9 +8899,8 @@
       <c r="B396" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C396" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C396" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D396" s="16"/>
       <c r="E396" s="12" t="s">
@@ -9303,9 +8914,8 @@
       <c r="B397" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C397" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C397" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D397" s="16"/>
       <c r="E397" s="12" t="s">
@@ -9319,9 +8929,8 @@
       <c r="B398" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C398" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C398" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D398" s="16"/>
       <c r="E398" s="12" t="s">
@@ -9335,9 +8944,8 @@
       <c r="B399" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C399" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C399" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D399" s="16"/>
       <c r="E399" s="12" t="s">
@@ -9351,9 +8959,8 @@
       <c r="B400" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C400" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C400" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D400" s="16"/>
       <c r="E400" s="12" t="s">
@@ -9367,9 +8974,8 @@
       <c r="B401" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C401" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C401" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D401" s="16"/>
       <c r="E401" s="12" t="s">
@@ -9383,9 +8989,8 @@
       <c r="B402" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C402" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C402" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D402" s="16"/>
       <c r="E402" s="12" t="s">
@@ -9399,9 +9004,8 @@
       <c r="B403" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="C403" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C403" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D403" s="16"/>
       <c r="E403" s="12" t="s">
@@ -9415,9 +9019,8 @@
       <c r="B404" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="C404" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C404" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D404" s="16"/>
       <c r="E404" s="12" t="s">
@@ -9431,9 +9034,8 @@
       <c r="B405" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="C405" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C405" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D405" s="16"/>
       <c r="E405" s="9" t="s">
@@ -9447,9 +9049,8 @@
       <c r="B406" s="11" t="s">
         <v>717</v>
       </c>
-      <c r="C406" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C406" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D406" s="16"/>
       <c r="E406" s="9" t="s">
@@ -9463,9 +9064,8 @@
       <c r="B407" s="11" t="s">
         <v>717</v>
       </c>
-      <c r="C407" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C407" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D407" s="16"/>
       <c r="E407" s="9" t="s">
@@ -9479,9 +9079,8 @@
       <c r="B408" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="C408" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C408" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D408" s="16"/>
       <c r="E408" s="9" t="s">
@@ -9495,9 +9094,8 @@
       <c r="B409" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="C409" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C409" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D409" s="16"/>
       <c r="E409" s="9" t="s">
@@ -9511,9 +9109,8 @@
       <c r="B410" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="C410" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C410" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D410" s="16"/>
       <c r="E410" s="9" t="s">
@@ -9527,9 +9124,8 @@
       <c r="B411" s="11" t="s">
         <v>717</v>
       </c>
-      <c r="C411" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C411" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D411" s="16"/>
       <c r="E411" s="9" t="s">
@@ -9543,9 +9139,8 @@
       <c r="B412" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="C412" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C412" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D412" s="16"/>
       <c r="E412" s="9" t="s">
@@ -9559,9 +9154,8 @@
       <c r="B413" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="C413" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C413" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D413" s="16"/>
       <c r="E413" s="9" t="s">
@@ -9575,9 +9169,8 @@
       <c r="B414" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="C414" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C414" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D414" s="16"/>
       <c r="E414" s="9" t="s">
@@ -9591,9 +9184,8 @@
       <c r="B415" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C415" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C415" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D415" s="16"/>
       <c r="E415" s="9" t="s">
@@ -9607,9 +9199,8 @@
       <c r="B416" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="C416" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C416" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D416" s="16"/>
       <c r="E416" s="9" t="s">
@@ -9623,9 +9214,8 @@
       <c r="B417" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="C417" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C417" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D417" s="16"/>
       <c r="E417" s="9" t="s">
@@ -9639,9 +9229,8 @@
       <c r="B418" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C418" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C418" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D418" s="16"/>
       <c r="E418" s="9" t="s">
@@ -9655,9 +9244,8 @@
       <c r="B419" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C419" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C419" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D419" s="16"/>
       <c r="E419" s="9" t="s">
@@ -9671,9 +9259,8 @@
       <c r="B420" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C420" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C420" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D420" s="16"/>
       <c r="E420" s="9" t="s">
@@ -9687,9 +9274,8 @@
       <c r="B421" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C421" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C421" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D421" s="16"/>
       <c r="E421" s="9" t="s">
@@ -9703,9 +9289,8 @@
       <c r="B422" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C422" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C422" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D422" s="16"/>
       <c r="E422" s="9" t="s">
@@ -9719,9 +9304,8 @@
       <c r="B423" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C423" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C423" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D423" s="16"/>
       <c r="E423" s="9" t="s">
@@ -9735,9 +9319,8 @@
       <c r="B424" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C424" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C424" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D424" s="16"/>
       <c r="E424" s="9" t="s">
@@ -9751,9 +9334,8 @@
       <c r="B425" s="11" t="s">
         <v>717</v>
       </c>
-      <c r="C425" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C425" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D425" s="16"/>
       <c r="E425" s="9" t="s">
@@ -9767,9 +9349,8 @@
       <c r="B426" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C426" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C426" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D426" s="16"/>
       <c r="E426" s="9" t="s">
@@ -9783,9 +9364,8 @@
       <c r="B427" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C427" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C427" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D427" s="16"/>
       <c r="E427" s="9" t="s">
@@ -9799,9 +9379,8 @@
       <c r="B428" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C428" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C428" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D428" s="16"/>
       <c r="E428" s="9" t="s">
@@ -9815,9 +9394,8 @@
       <c r="B429" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C429" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C429" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D429" s="16"/>
       <c r="E429" s="9" t="s">
@@ -9831,9 +9409,8 @@
       <c r="B430" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C430" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C430" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D430" s="16"/>
       <c r="E430" s="9" t="s">
@@ -9847,9 +9424,8 @@
       <c r="B431" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C431" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C431" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D431" s="16"/>
       <c r="E431" s="9" t="s">
@@ -9863,9 +9439,8 @@
       <c r="B432" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C432" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C432" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D432" s="16"/>
       <c r="E432" s="9" t="s">
@@ -9879,9 +9454,8 @@
       <c r="B433" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C433" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C433" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D433" s="16"/>
       <c r="E433" s="9" t="s">
@@ -9895,9 +9469,8 @@
       <c r="B434" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C434" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C434" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D434" s="16"/>
       <c r="E434" s="9" t="s">
@@ -9911,9 +9484,8 @@
       <c r="B435" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C435" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C435" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D435" s="16"/>
       <c r="E435" s="9" t="s">
@@ -9927,9 +9499,8 @@
       <c r="B436" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C436" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C436" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D436" s="16"/>
       <c r="E436" s="9" t="s">
@@ -9943,9 +9514,8 @@
       <c r="B437" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C437" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C437" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D437" s="16"/>
       <c r="E437" s="9" t="s">
@@ -9959,9 +9529,8 @@
       <c r="B438" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C438" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C438" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D438" s="16"/>
       <c r="E438" s="9" t="s">
@@ -9975,9 +9544,8 @@
       <c r="B439" s="10" t="s">
         <v>718</v>
       </c>
-      <c r="C439" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C439" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D439" s="16"/>
       <c r="E439" s="12" t="s">
@@ -9991,9 +9559,8 @@
       <c r="B440" s="10" t="s">
         <v>718</v>
       </c>
-      <c r="C440" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C440" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D440" s="16"/>
       <c r="E440" s="12" t="s">
@@ -10007,9 +9574,8 @@
       <c r="B441" s="10" t="s">
         <v>719</v>
       </c>
-      <c r="C441" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C441" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D441" s="16"/>
       <c r="E441" s="12" t="s">
@@ -10023,9 +9589,8 @@
       <c r="B442" s="10" t="s">
         <v>719</v>
       </c>
-      <c r="C442" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C442" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D442" s="16"/>
       <c r="E442" s="12" t="s">
@@ -10039,9 +9604,8 @@
       <c r="B443" s="10" t="s">
         <v>718</v>
       </c>
-      <c r="C443" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C443" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D443" s="16"/>
       <c r="E443" s="12" t="s">
@@ -10055,9 +9619,8 @@
       <c r="B444" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C444" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C444" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D444" s="16"/>
       <c r="E444" s="12" t="s">
@@ -10071,9 +9634,8 @@
       <c r="B445" s="10" t="s">
         <v>719</v>
       </c>
-      <c r="C445" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C445" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D445" s="16"/>
       <c r="E445" s="12" t="s">
@@ -10087,9 +9649,8 @@
       <c r="B446" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C446" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C446" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D446" s="16"/>
       <c r="E446" s="12" t="s">
@@ -10103,9 +9664,8 @@
       <c r="B447" s="10" t="s">
         <v>719</v>
       </c>
-      <c r="C447" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C447" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D447" s="16"/>
       <c r="E447" s="12" t="s">
@@ -10119,9 +9679,8 @@
       <c r="B448" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C448" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C448" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D448" s="16"/>
       <c r="E448" s="12" t="s">
@@ -10135,9 +9694,8 @@
       <c r="B449" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C449" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C449" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D449" s="16"/>
       <c r="E449" s="12" t="s">
@@ -10151,9 +9709,8 @@
       <c r="B450" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C450" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C450" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D450" s="16"/>
       <c r="E450" s="12" t="s">
@@ -10167,9 +9724,8 @@
       <c r="B451" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C451" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C451" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D451" s="16"/>
       <c r="E451" s="12" t="s">
@@ -10183,9 +9739,8 @@
       <c r="B452" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C452" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C452" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D452" s="16"/>
       <c r="E452" s="12" t="s">
@@ -10199,9 +9754,8 @@
       <c r="B453" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C453" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C453" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D453" s="16"/>
       <c r="E453" s="12" t="s">
@@ -10215,9 +9769,8 @@
       <c r="B454" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C454" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C454" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D454" s="16"/>
       <c r="E454" s="12" t="s">
@@ -10231,9 +9784,8 @@
       <c r="B455" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C455" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C455" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D455" s="16"/>
       <c r="E455" s="12" t="s">
@@ -10247,9 +9799,8 @@
       <c r="B456" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C456" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C456" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D456" s="16"/>
       <c r="E456" s="12" t="s">
@@ -10263,9 +9814,8 @@
       <c r="B457" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C457" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C457" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D457" s="16"/>
       <c r="E457" s="12" t="s">
@@ -10279,9 +9829,8 @@
       <c r="B458" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C458" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C458" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D458" s="16"/>
       <c r="E458" s="12" t="s">
@@ -10295,9 +9844,8 @@
       <c r="B459" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C459" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C459" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D459" s="16"/>
       <c r="E459" s="12" t="s">
@@ -10311,9 +9859,8 @@
       <c r="B460" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C460" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C460" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D460" s="16"/>
       <c r="E460" s="12" t="s">
@@ -10327,9 +9874,8 @@
       <c r="B461" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C461" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C461" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D461" s="16"/>
       <c r="E461" s="12" t="s">
@@ -10343,9 +9889,8 @@
       <c r="B462" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C462" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C462" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D462" s="16"/>
       <c r="E462" s="12" t="s">
@@ -10359,9 +9904,8 @@
       <c r="B463" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C463" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C463" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D463" s="16"/>
       <c r="E463" s="12" t="s">
@@ -10375,9 +9919,8 @@
       <c r="B464" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C464" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C464" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D464" s="16"/>
       <c r="E464" s="12" t="s">
@@ -10391,9 +9934,8 @@
       <c r="B465" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C465" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C465" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D465" s="16"/>
       <c r="E465" s="12" t="s">
@@ -10407,9 +9949,8 @@
       <c r="B466" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C466" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C466" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D466" s="16"/>
       <c r="E466" s="12" t="s">
@@ -10423,9 +9964,8 @@
       <c r="B467" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C467" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C467" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D467" s="16"/>
       <c r="E467" s="12" t="s">
@@ -10439,9 +9979,8 @@
       <c r="B468" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C468" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C468" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D468" s="16"/>
       <c r="E468" s="12" t="s">
@@ -10455,9 +9994,8 @@
       <c r="B469" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C469" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C469" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D469" s="16"/>
       <c r="E469" s="12" t="s">
@@ -10471,9 +10009,8 @@
       <c r="B470" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C470" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C470" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D470" s="16"/>
       <c r="E470" s="12" t="s">
@@ -10487,9 +10024,8 @@
       <c r="B471" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C471" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C471" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D471" s="16"/>
       <c r="E471" s="12" t="s">
@@ -10503,9 +10039,8 @@
       <c r="B472" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C472" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C472" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D472" s="16"/>
       <c r="E472" s="12" t="s">
@@ -10519,9 +10054,8 @@
       <c r="B473" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C473" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C473" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D473" s="16"/>
       <c r="E473" s="12" t="s">
@@ -10535,9 +10069,8 @@
       <c r="B474" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C474" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C474" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D474" s="16"/>
       <c r="E474" s="12" t="s">
@@ -10551,9 +10084,8 @@
       <c r="B475" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C475" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C475" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D475" s="16"/>
       <c r="E475" s="12" t="s">
@@ -10567,9 +10099,8 @@
       <c r="B476" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C476" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C476" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D476" s="16"/>
       <c r="E476" s="12" t="s">
@@ -10583,9 +10114,8 @@
       <c r="B477" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C477" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C477" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D477" s="16"/>
       <c r="E477" s="12" t="s">
@@ -10599,9 +10129,8 @@
       <c r="B478" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C478" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C478" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D478" s="16"/>
       <c r="E478" s="12" t="s">
@@ -10615,9 +10144,8 @@
       <c r="B479" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C479" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C479" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D479" s="16"/>
       <c r="E479" s="12" t="s">
@@ -10631,9 +10159,8 @@
       <c r="B480" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C480" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C480" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D480" s="16"/>
       <c r="E480" s="12" t="s">
@@ -10647,9 +10174,8 @@
       <c r="B481" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C481" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C481" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D481" s="16"/>
       <c r="E481" s="12" t="s">
@@ -10663,9 +10189,8 @@
       <c r="B482" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="C482" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C482" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D482" s="16"/>
       <c r="E482" s="12" t="s">
@@ -10679,9 +10204,8 @@
       <c r="B483" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C483" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C483" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D483" s="16"/>
       <c r="E483" s="9" t="s">
@@ -10695,9 +10219,8 @@
       <c r="B484" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C484" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C484" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D484" s="16"/>
       <c r="E484" s="9" t="s">
@@ -10711,9 +10234,8 @@
       <c r="B485" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C485" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C485" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D485" s="16"/>
       <c r="E485" s="9" t="s">
@@ -10727,9 +10249,8 @@
       <c r="B486" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C486" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C486" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D486" s="16"/>
       <c r="E486" s="9" t="s">
@@ -10743,9 +10264,8 @@
       <c r="B487" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C487" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C487" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D487" s="16"/>
       <c r="E487" s="9" t="s">
@@ -10759,9 +10279,8 @@
       <c r="B488" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C488" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C488" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D488" s="16"/>
       <c r="E488" s="9" t="s">
@@ -10775,9 +10294,8 @@
       <c r="B489" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C489" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C489" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D489" s="16"/>
       <c r="E489" s="9" t="s">
@@ -10791,9 +10309,8 @@
       <c r="B490" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C490" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C490" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D490" s="16"/>
       <c r="E490" s="9" t="s">
@@ -10807,9 +10324,8 @@
       <c r="B491" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C491" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C491" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D491" s="16"/>
       <c r="E491" s="9" t="s">
@@ -10823,9 +10339,8 @@
       <c r="B492" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C492" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C492" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D492" s="16"/>
       <c r="E492" s="9" t="s">
@@ -10839,9 +10354,8 @@
       <c r="B493" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C493" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C493" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D493" s="16"/>
       <c r="E493" s="9" t="s">
@@ -10855,9 +10369,8 @@
       <c r="B494" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C494" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C494" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D494" s="16"/>
       <c r="E494" s="9" t="s">
@@ -10871,9 +10384,8 @@
       <c r="B495" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C495" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C495" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D495" s="16"/>
       <c r="E495" s="9" t="s">
@@ -10887,9 +10399,8 @@
       <c r="B496" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C496" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C496" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D496" s="16"/>
       <c r="E496" s="9" t="s">
@@ -10903,9 +10414,8 @@
       <c r="B497" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C497" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C497" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D497" s="16"/>
       <c r="E497" s="9" t="s">
@@ -10919,9 +10429,8 @@
       <c r="B498" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C498" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C498" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D498" s="16"/>
       <c r="E498" s="9" t="s">
@@ -10935,9 +10444,8 @@
       <c r="B499" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C499" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C499" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D499" s="16"/>
       <c r="E499" s="9" t="s">
@@ -10951,9 +10459,8 @@
       <c r="B500" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C500" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C500" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D500" s="16"/>
       <c r="E500" s="9" t="s">
@@ -10967,9 +10474,8 @@
       <c r="B501" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C501" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C501" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D501" s="16"/>
       <c r="E501" s="9" t="s">
@@ -10983,9 +10489,8 @@
       <c r="B502" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C502" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C502" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D502" s="16"/>
       <c r="E502" s="9" t="s">
@@ -10999,9 +10504,8 @@
       <c r="B503" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C503" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C503" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D503" s="16"/>
       <c r="E503" s="9" t="s">
@@ -11015,9 +10519,8 @@
       <c r="B504" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C504" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C504" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D504" s="16"/>
       <c r="E504" s="9" t="s">
@@ -11031,9 +10534,8 @@
       <c r="B505" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C505" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C505" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D505" s="16"/>
       <c r="E505" s="9" t="s">
@@ -11047,9 +10549,8 @@
       <c r="B506" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C506" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C506" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D506" s="16"/>
       <c r="E506" s="9" t="s">
@@ -11063,9 +10564,8 @@
       <c r="B507" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C507" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C507" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D507" s="16"/>
       <c r="E507" s="9" t="s">
@@ -11079,9 +10579,8 @@
       <c r="B508" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C508" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C508" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D508" s="16"/>
       <c r="E508" s="9" t="s">
@@ -11095,9 +10594,8 @@
       <c r="B509" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C509" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C509" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D509" s="16"/>
       <c r="E509" s="9" t="s">
@@ -11111,9 +10609,8 @@
       <c r="B510" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C510" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C510" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D510" s="16"/>
       <c r="E510" s="9" t="s">
@@ -11127,9 +10624,8 @@
       <c r="B511" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C511" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C511" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D511" s="16"/>
       <c r="E511" s="9" t="s">
@@ -11143,9 +10639,8 @@
       <c r="B512" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C512" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C512" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D512" s="16"/>
       <c r="E512" s="9" t="s">
@@ -11159,9 +10654,8 @@
       <c r="B513" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C513" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C513" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D513" s="16"/>
       <c r="E513" s="9" t="s">
@@ -11175,9 +10669,8 @@
       <c r="B514" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C514" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C514" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D514" s="16"/>
       <c r="E514" s="9" t="s">
@@ -11191,9 +10684,8 @@
       <c r="B515" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C515" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C515" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D515" s="16"/>
       <c r="E515" s="9" t="s">
@@ -11207,9 +10699,8 @@
       <c r="B516" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C516" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C516" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D516" s="16"/>
       <c r="E516" s="9" t="s">
@@ -11223,9 +10714,8 @@
       <c r="B517" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C517" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C517" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D517" s="16"/>
       <c r="E517" s="9" t="s">
@@ -11239,9 +10729,8 @@
       <c r="B518" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C518" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C518" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D518" s="16"/>
       <c r="E518" s="9" t="s">
@@ -11255,9 +10744,8 @@
       <c r="B519" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C519" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C519" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D519" s="16"/>
       <c r="E519" s="9" t="s">
@@ -11271,9 +10759,8 @@
       <c r="B520" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C520" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C520" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D520" s="16"/>
       <c r="E520" s="9" t="s">
@@ -11287,9 +10774,8 @@
       <c r="B521" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="C521" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C521" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D521" s="16"/>
       <c r="E521" s="9" t="s">
@@ -11303,9 +10789,8 @@
       <c r="B522" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C522" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C522" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D522" s="16"/>
       <c r="E522" s="9" t="s">
@@ -11319,9 +10804,8 @@
       <c r="B523" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="C523" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C523" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D523" s="16"/>
       <c r="E523" s="9" t="s">
@@ -11335,9 +10819,8 @@
       <c r="B524" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C524" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C524" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D524" s="16"/>
       <c r="E524" s="9" t="s">
@@ -11351,9 +10834,8 @@
       <c r="B525" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C525" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C525" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D525" s="16"/>
       <c r="E525" s="9" t="s">
@@ -11367,9 +10849,8 @@
       <c r="B526" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C526" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C526" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D526" s="16"/>
       <c r="E526" s="9" t="s">
@@ -11383,9 +10864,8 @@
       <c r="B527" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C527" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C527" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D527" s="16"/>
       <c r="E527" s="9" t="s">
@@ -11399,9 +10879,8 @@
       <c r="B528" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C528" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C528" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D528" s="16"/>
       <c r="E528" s="9" t="s">
@@ -11415,9 +10894,8 @@
       <c r="B529" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C529" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C529" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D529" s="16"/>
       <c r="E529" s="9" t="s">
@@ -11431,9 +10909,8 @@
       <c r="B530" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C530" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C530" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D530" s="16"/>
       <c r="E530" s="9" t="s">
@@ -11447,9 +10924,8 @@
       <c r="B531" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C531" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C531" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D531" s="16"/>
       <c r="E531" s="9" t="s">
@@ -11463,9 +10939,8 @@
       <c r="B532" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C532" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C532" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D532" s="16"/>
       <c r="E532" s="9" t="s">
@@ -11479,9 +10954,8 @@
       <c r="B533" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C533" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C533" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D533" s="16"/>
       <c r="E533" s="9" t="s">
@@ -11495,9 +10969,8 @@
       <c r="B534" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C534" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C534" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D534" s="16"/>
       <c r="E534" s="9" t="s">
@@ -11511,9 +10984,8 @@
       <c r="B535" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C535" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C535" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D535" s="16"/>
       <c r="E535" s="9" t="s">
@@ -11527,9 +10999,8 @@
       <c r="B536" s="11" t="s">
         <v>717</v>
       </c>
-      <c r="C536" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C536" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D536" s="16"/>
       <c r="E536" s="9" t="s">
@@ -11543,9 +11014,8 @@
       <c r="B537" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C537" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C537" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D537" s="16"/>
       <c r="E537" s="9" t="s">
@@ -11559,9 +11029,8 @@
       <c r="B538" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C538" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C538" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D538" s="16"/>
       <c r="E538" s="9" t="s">
@@ -11575,9 +11044,8 @@
       <c r="B539" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C539" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C539" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D539" s="16"/>
       <c r="E539" s="9" t="s">
@@ -11591,9 +11059,8 @@
       <c r="B540" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C540" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C540" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D540" s="16"/>
       <c r="E540" s="9" t="s">
@@ -11607,9 +11074,8 @@
       <c r="B541" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C541" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C541" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D541" s="16"/>
       <c r="E541" s="9" t="s">
@@ -11623,9 +11089,8 @@
       <c r="B542" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C542" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C542" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D542" s="16"/>
       <c r="E542" s="9" t="s">
@@ -11639,9 +11104,8 @@
       <c r="B543" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C543" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C543" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D543" s="16"/>
       <c r="E543" s="9" t="s">
@@ -11655,9 +11119,8 @@
       <c r="B544" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C544" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C544" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D544" s="16"/>
       <c r="E544" s="9" t="s">
@@ -11671,9 +11134,8 @@
       <c r="B545" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C545" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C545" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D545" s="16"/>
       <c r="E545" s="9" t="s">
@@ -11687,9 +11149,8 @@
       <c r="B546" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C546" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C546" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D546" s="16"/>
       <c r="E546" s="9" t="s">
@@ -11703,9 +11164,8 @@
       <c r="B547" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C547" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C547" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D547" s="16"/>
       <c r="E547" s="9" t="s">
@@ -11719,9 +11179,8 @@
       <c r="B548" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C548" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C548" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D548" s="16"/>
       <c r="E548" s="9" t="s">
@@ -11735,9 +11194,8 @@
       <c r="B549" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C549" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C549" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D549" s="16"/>
       <c r="E549" s="9" t="s">
@@ -11751,9 +11209,8 @@
       <c r="B550" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C550" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C550" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D550" s="16"/>
       <c r="E550" s="9" t="s">
@@ -11767,9 +11224,8 @@
       <c r="B551" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C551" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C551" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D551" s="16"/>
       <c r="E551" s="9" t="s">
@@ -11783,9 +11239,8 @@
       <c r="B552" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C552" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C552" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D552" s="16"/>
       <c r="E552" s="9" t="s">
@@ -11799,9 +11254,8 @@
       <c r="B553" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C553" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C553" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D553" s="16"/>
       <c r="E553" s="9" t="s">
@@ -11815,9 +11269,8 @@
       <c r="B554" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C554" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C554" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D554" s="16"/>
       <c r="E554" s="9" t="s">
@@ -11831,9 +11284,8 @@
       <c r="B555" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C555" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C555" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D555" s="16"/>
       <c r="E555" s="9" t="s">
@@ -11847,9 +11299,8 @@
       <c r="B556" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C556" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C556" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D556" s="16"/>
       <c r="E556" s="9" t="s">
@@ -11863,9 +11314,8 @@
       <c r="B557" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C557" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C557" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D557" s="16"/>
       <c r="E557" s="9" t="s">
@@ -11879,9 +11329,8 @@
       <c r="B558" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C558" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C558" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D558" s="16"/>
       <c r="E558" s="9" t="s">
@@ -11895,9 +11344,8 @@
       <c r="B559" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C559" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C559" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D559" s="16"/>
       <c r="E559" s="9" t="s">
@@ -11911,9 +11359,8 @@
       <c r="B560" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C560" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C560" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D560" s="16"/>
       <c r="E560" s="9" t="s">
@@ -11927,9 +11374,8 @@
       <c r="B561" s="11" t="s">
         <v>717</v>
       </c>
-      <c r="C561" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C561" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D561" s="16"/>
       <c r="E561" s="9" t="s">
@@ -11943,9 +11389,8 @@
       <c r="B562" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C562" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C562" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D562" s="16"/>
       <c r="E562" s="9" t="s">
@@ -11959,9 +11404,8 @@
       <c r="B563" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C563" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C563" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D563" s="16"/>
       <c r="E563" s="9" t="s">
@@ -11975,9 +11419,8 @@
       <c r="B564" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C564" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C564" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D564" s="16"/>
       <c r="E564" s="9" t="s">
@@ -11991,9 +11434,8 @@
       <c r="B565" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C565" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C565" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D565" s="16"/>
       <c r="E565" s="9" t="s">
@@ -12007,9 +11449,8 @@
       <c r="B566" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C566" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C566" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D566" s="16"/>
       <c r="E566" s="9" t="s">
@@ -12023,9 +11464,8 @@
       <c r="B567" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C567" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C567" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D567" s="16"/>
       <c r="E567" s="9" t="s">
@@ -12039,9 +11479,8 @@
       <c r="B568" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C568" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C568" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D568" s="16"/>
       <c r="E568" s="9" t="s">
@@ -12055,9 +11494,8 @@
       <c r="B569" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C569" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C569" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D569" s="16"/>
       <c r="E569" s="9" t="s">
@@ -12071,9 +11509,8 @@
       <c r="B570" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C570" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C570" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D570" s="16"/>
       <c r="E570" s="9" t="s">
@@ -12087,9 +11524,8 @@
       <c r="B571" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C571" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C571" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D571" s="16"/>
       <c r="E571" s="9" t="s">
@@ -12103,9 +11539,8 @@
       <c r="B572" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C572" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C572" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D572" s="16"/>
       <c r="E572" s="9" t="s">
@@ -12119,9 +11554,8 @@
       <c r="B573" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C573" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C573" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D573" s="16"/>
       <c r="E573" s="12" t="s">
@@ -12135,9 +11569,8 @@
       <c r="B574" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C574" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C574" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D574" s="16"/>
       <c r="E574" s="12" t="s">
@@ -12151,9 +11584,8 @@
       <c r="B575" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C575" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C575" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D575" s="16"/>
       <c r="E575" s="12" t="s">
@@ -12167,9 +11599,8 @@
       <c r="B576" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C576" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C576" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D576" s="16"/>
       <c r="E576" s="12" t="s">
@@ -12183,9 +11614,8 @@
       <c r="B577" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C577" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C577" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D577" s="16"/>
       <c r="E577" s="12" t="s">
@@ -12199,9 +11629,8 @@
       <c r="B578" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C578" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C578" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D578" s="16"/>
       <c r="E578" s="12" t="s">
@@ -12215,9 +11644,8 @@
       <c r="B579" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C579" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C579" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D579" s="16"/>
       <c r="E579" s="12" t="s">
@@ -12231,9 +11659,8 @@
       <c r="B580" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C580" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C580" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D580" s="16"/>
       <c r="E580" s="12" t="s">
@@ -12247,9 +11674,8 @@
       <c r="B581" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C581" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C581" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D581" s="16"/>
       <c r="E581" s="12" t="s">
@@ -12263,9 +11689,8 @@
       <c r="B582" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C582" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C582" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D582" s="16"/>
       <c r="E582" s="12" t="s">
@@ -12279,9 +11704,8 @@
       <c r="B583" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C583" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C583" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D583" s="16"/>
       <c r="E583" s="12" t="s">
@@ -12295,9 +11719,8 @@
       <c r="B584" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C584" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C584" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D584" s="16"/>
       <c r="E584" s="12" t="s">
@@ -12311,9 +11734,8 @@
       <c r="B585" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C585" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C585" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D585" s="16"/>
       <c r="E585" s="12" t="s">
@@ -12327,9 +11749,8 @@
       <c r="B586" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C586" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C586" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D586" s="16"/>
       <c r="E586" s="12" t="s">
@@ -12343,9 +11764,8 @@
       <c r="B587" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C587" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C587" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D587" s="16"/>
       <c r="E587" s="12" t="s">
@@ -12359,9 +11779,8 @@
       <c r="B588" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C588" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C588" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D588" s="16"/>
       <c r="E588" s="12" t="s">
@@ -12375,9 +11794,8 @@
       <c r="B589" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C589" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C589" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D589" s="16"/>
       <c r="E589" s="12" t="s">
@@ -12391,9 +11809,8 @@
       <c r="B590" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="C590" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C590" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D590" s="16"/>
       <c r="E590" s="12" t="s">
@@ -12407,9 +11824,8 @@
       <c r="B591" s="11" t="s">
         <v>717</v>
       </c>
-      <c r="C591" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C591" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D591" s="16"/>
       <c r="E591" s="12" t="s">
@@ -12423,9 +11839,8 @@
       <c r="B592" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="C592" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C592" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D592" s="16"/>
       <c r="E592" s="12" t="s">
@@ -12439,9 +11854,8 @@
       <c r="B593" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C593" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C593" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D593" s="16"/>
       <c r="E593" s="9" t="s">
@@ -12455,9 +11869,8 @@
       <c r="B594" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C594" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C594" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D594" s="16"/>
       <c r="E594" s="9" t="s">
@@ -12471,9 +11884,8 @@
       <c r="B595" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C595" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C595" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D595" s="16"/>
       <c r="E595" s="9" t="s">
@@ -12487,9 +11899,8 @@
       <c r="B596" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C596" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C596" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D596" s="16"/>
       <c r="E596" s="9" t="s">
@@ -12503,9 +11914,8 @@
       <c r="B597" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C597" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C597" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D597" s="16"/>
       <c r="E597" s="9" t="s">
@@ -12519,9 +11929,8 @@
       <c r="B598" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C598" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C598" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D598" s="16"/>
       <c r="E598" s="9" t="s">
@@ -12535,9 +11944,8 @@
       <c r="B599" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C599" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C599" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D599" s="16"/>
       <c r="E599" s="9" t="s">
@@ -12551,9 +11959,8 @@
       <c r="B600" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C600" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C600" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D600" s="16"/>
       <c r="E600" s="9" t="s">
@@ -12567,9 +11974,8 @@
       <c r="B601" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C601" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C601" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D601" s="16"/>
       <c r="E601" s="9" t="s">
@@ -12583,9 +11989,8 @@
       <c r="B602" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="C602" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C602" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D602" s="16"/>
       <c r="E602" s="9" t="s">
@@ -12599,9 +12004,8 @@
       <c r="B603" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C603" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C603" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D603" s="16"/>
       <c r="E603" s="9" t="s">
@@ -12615,9 +12019,8 @@
       <c r="B604" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C604" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C604" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D604" s="16"/>
       <c r="E604" s="9" t="s">
@@ -12631,9 +12034,8 @@
       <c r="B605" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C605" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C605" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D605" s="16"/>
       <c r="E605" s="9" t="s">
@@ -12647,9 +12049,8 @@
       <c r="B606" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C606" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C606" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D606" s="16"/>
       <c r="E606" s="9" t="s">
@@ -12663,9 +12064,8 @@
       <c r="B607" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C607" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C607" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D607" s="16"/>
       <c r="E607" s="9" t="s">
@@ -12679,9 +12079,8 @@
       <c r="B608" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C608" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C608" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D608" s="16"/>
       <c r="E608" s="9" t="s">
@@ -12695,9 +12094,8 @@
       <c r="B609" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C609" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C609" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D609" s="16"/>
       <c r="E609" s="9" t="s">
@@ -12711,9 +12109,8 @@
       <c r="B610" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C610" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C610" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D610" s="16"/>
       <c r="E610" s="9" t="s">
@@ -12727,9 +12124,8 @@
       <c r="B611" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C611" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C611" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D611" s="16"/>
       <c r="E611" s="9" t="s">
@@ -12743,9 +12139,8 @@
       <c r="B612" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C612" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C612" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D612" s="16"/>
       <c r="E612" s="9" t="s">
@@ -12759,9 +12154,8 @@
       <c r="B613" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C613" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C613" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D613" s="16"/>
       <c r="E613" s="9" t="s">
@@ -12775,9 +12169,8 @@
       <c r="B614" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C614" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C614" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D614" s="16"/>
       <c r="E614" s="9" t="s">
@@ -12791,9 +12184,8 @@
       <c r="B615" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C615" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C615" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D615" s="16"/>
       <c r="E615" s="9" t="s">
@@ -12807,9 +12199,8 @@
       <c r="B616" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C616" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C616" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D616" s="16"/>
       <c r="E616" s="9" t="s">
@@ -12823,9 +12214,8 @@
       <c r="B617" s="13" t="s">
         <v>717</v>
       </c>
-      <c r="C617" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C617" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D617" s="16"/>
       <c r="E617" s="9" t="s">
@@ -12839,9 +12229,8 @@
       <c r="B618" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="C618" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C618" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D618" s="16"/>
       <c r="E618" s="9" t="s">
@@ -12855,9 +12244,8 @@
       <c r="B619" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C619" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C619" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D619" s="16"/>
       <c r="E619" s="9" t="s">
@@ -12871,9 +12259,8 @@
       <c r="B620" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C620" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C620" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D620" s="16"/>
       <c r="E620" s="9" t="s">
@@ -12887,9 +12274,8 @@
       <c r="B621" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C621" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C621" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D621" s="16"/>
       <c r="E621" s="9" t="s">
@@ -12903,9 +12289,8 @@
       <c r="B622" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C622" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C622" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D622" s="16"/>
       <c r="E622" s="9" t="s">
@@ -12919,9 +12304,8 @@
       <c r="B623" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C623" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C623" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D623" s="16"/>
       <c r="E623" s="9" t="s">
@@ -12935,9 +12319,8 @@
       <c r="B624" s="13" t="s">
         <v>717</v>
       </c>
-      <c r="C624" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C624" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D624" s="16"/>
       <c r="E624" s="9" t="s">
@@ -12951,9 +12334,8 @@
       <c r="B625" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C625" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C625" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D625" s="16"/>
       <c r="E625" s="9" t="s">
@@ -12967,9 +12349,8 @@
       <c r="B626" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C626" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C626" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D626" s="16"/>
       <c r="E626" s="9" t="s">
@@ -12983,9 +12364,8 @@
       <c r="B627" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C627" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C627" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D627" s="16"/>
       <c r="E627" s="9" t="s">
@@ -12999,9 +12379,8 @@
       <c r="B628" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C628" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C628" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D628" s="16"/>
       <c r="E628" s="9" t="s">
@@ -13015,9 +12394,8 @@
       <c r="B629" s="13" t="s">
         <v>717</v>
       </c>
-      <c r="C629" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C629" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D629" s="16"/>
       <c r="E629" s="9" t="s">
@@ -13031,9 +12409,8 @@
       <c r="B630" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C630" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C630" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D630" s="16"/>
       <c r="E630" s="9" t="s">
@@ -13047,9 +12424,8 @@
       <c r="B631" s="13" t="s">
         <v>717</v>
       </c>
-      <c r="C631" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C631" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D631" s="16"/>
       <c r="E631" s="9" t="s">
@@ -13063,9 +12439,8 @@
       <c r="B632" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C632" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C632" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D632" s="16"/>
       <c r="E632" s="9" t="s">
@@ -13079,9 +12454,8 @@
       <c r="B633" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C633" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C633" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D633" s="16"/>
       <c r="E633" s="9" t="s">
@@ -13095,9 +12469,8 @@
       <c r="B634" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C634" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C634" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D634" s="16"/>
       <c r="E634" s="9" t="s">
@@ -13111,9 +12484,8 @@
       <c r="B635" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C635" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C635" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D635" s="16"/>
       <c r="E635" s="9" t="s">
@@ -13127,9 +12499,8 @@
       <c r="B636" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C636" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C636" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D636" s="16"/>
       <c r="E636" s="9" t="s">
@@ -13143,9 +12514,8 @@
       <c r="B637" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C637" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C637" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D637" s="16"/>
       <c r="E637" s="9" t="s">
@@ -13159,9 +12529,8 @@
       <c r="B638" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C638" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C638" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D638" s="16"/>
       <c r="E638" s="9" t="s">
@@ -13175,9 +12544,8 @@
       <c r="B639" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C639" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C639" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D639" s="16"/>
       <c r="E639" s="9" t="s">
@@ -13191,9 +12559,8 @@
       <c r="B640" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C640" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C640" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D640" s="16"/>
       <c r="E640" s="9" t="s">
@@ -13207,9 +12574,8 @@
       <c r="B641" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="C641" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C641" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D641" s="16"/>
       <c r="E641" s="9" t="s">
@@ -13223,9 +12589,8 @@
       <c r="B642" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C642" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C642" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D642" s="16"/>
       <c r="E642" s="9" t="s">
@@ -13239,9 +12604,8 @@
       <c r="B643" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C643" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C643" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D643" s="16"/>
       <c r="E643" s="9" t="s">
@@ -13255,9 +12619,8 @@
       <c r="B644" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C644" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C644" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D644" s="16"/>
       <c r="E644" s="9" t="s">
@@ -13271,9 +12634,8 @@
       <c r="B645" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C645" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C645" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D645" s="16"/>
       <c r="E645" s="9" t="s">
@@ -13287,9 +12649,8 @@
       <c r="B646" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C646" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C646" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D646" s="16"/>
       <c r="E646" s="12" t="s">
@@ -13303,9 +12664,8 @@
       <c r="B647" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C647" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C647" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D647" s="16"/>
       <c r="E647" s="9" t="s">
@@ -13319,9 +12679,8 @@
       <c r="B648" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C648" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C648" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D648" s="16"/>
       <c r="E648" s="9" t="s">
@@ -13335,9 +12694,8 @@
       <c r="B649" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C649" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C649" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D649" s="16"/>
       <c r="E649" s="9" t="s">
@@ -13351,9 +12709,8 @@
       <c r="B650" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C650" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C650" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D650" s="16"/>
       <c r="E650" s="9" t="s">
@@ -13367,9 +12724,8 @@
       <c r="B651" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C651" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C651" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D651" s="16"/>
       <c r="E651" s="9" t="s">
@@ -13383,9 +12739,8 @@
       <c r="B652" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C652" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C652" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D652" s="16"/>
       <c r="E652" s="9" t="s">
@@ -13399,9 +12754,8 @@
       <c r="B653" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C653" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C653" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D653" s="16"/>
       <c r="E653" s="9" t="s">
@@ -13415,9 +12769,8 @@
       <c r="B654" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C654" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C654" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D654" s="16"/>
       <c r="E654" s="9" t="s">
@@ -13431,9 +12784,8 @@
       <c r="B655" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C655" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C655" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D655" s="16"/>
       <c r="E655" s="9" t="s">
@@ -13447,9 +12799,8 @@
       <c r="B656" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C656" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C656" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D656" s="16"/>
       <c r="E656" s="9" t="s">
@@ -13463,9 +12814,8 @@
       <c r="B657" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C657" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C657" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D657" s="16"/>
       <c r="E657" s="9" t="s">
@@ -13479,9 +12829,8 @@
       <c r="B658" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C658" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C658" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D658" s="16"/>
       <c r="E658" s="9" t="s">
@@ -13495,9 +12844,8 @@
       <c r="B659" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="C659" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C659" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D659" s="16"/>
       <c r="E659" s="9" t="s">
@@ -13511,9 +12859,8 @@
       <c r="B660" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C660" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C660" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D660" s="16"/>
       <c r="E660" s="9" t="s">
@@ -13527,9 +12874,8 @@
       <c r="B661" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C661" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C661" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D661" s="16"/>
       <c r="E661" s="9" t="s">
@@ -13543,9 +12889,8 @@
       <c r="B662" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C662" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C662" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D662" s="16"/>
       <c r="E662" s="9" t="s">
@@ -13559,9 +12904,8 @@
       <c r="B663" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C663" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C663" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D663" s="16"/>
       <c r="E663" s="9" t="s">
@@ -13575,9 +12919,8 @@
       <c r="B664" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C664" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C664" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D664" s="16"/>
       <c r="E664" s="9" t="s">
@@ -13591,9 +12934,8 @@
       <c r="B665" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C665" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C665" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D665" s="16"/>
       <c r="E665" s="9" t="s">
@@ -13607,9 +12949,8 @@
       <c r="B666" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C666" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C666" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D666" s="16"/>
       <c r="E666" s="9" t="s">
@@ -13623,9 +12964,8 @@
       <c r="B667" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C667" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C667" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D667" s="16"/>
       <c r="E667" s="9" t="s">
@@ -13639,9 +12979,8 @@
       <c r="B668" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C668" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C668" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D668" s="16"/>
       <c r="E668" s="9" t="s">
@@ -13655,9 +12994,8 @@
       <c r="B669" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C669" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C669" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D669" s="16"/>
       <c r="E669" s="9" t="s">
@@ -13671,9 +13009,8 @@
       <c r="B670" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C670" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C670" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D670" s="16"/>
       <c r="E670" s="9" t="s">
@@ -13687,9 +13024,8 @@
       <c r="B671" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C671" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C671" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D671" s="16"/>
       <c r="E671" s="9" t="s">
@@ -13703,9 +13039,8 @@
       <c r="B672" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C672" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C672" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D672" s="16"/>
       <c r="E672" s="9" t="s">
@@ -13719,9 +13054,8 @@
       <c r="B673" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C673" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C673" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D673" s="16"/>
       <c r="E673" s="9" t="s">
@@ -13735,9 +13069,8 @@
       <c r="B674" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="C674" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C674" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D674" s="16"/>
       <c r="E674" s="9" t="s">
@@ -13751,9 +13084,8 @@
       <c r="B675" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C675" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C675" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D675" s="16"/>
       <c r="E675" s="9" t="s">
@@ -13767,9 +13099,8 @@
       <c r="B676" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C676" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C676" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D676" s="16"/>
       <c r="E676" s="9" t="s">
@@ -13783,9 +13114,8 @@
       <c r="B677" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C677" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C677" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D677" s="16"/>
       <c r="E677" s="9" t="s">
@@ -13799,9 +13129,8 @@
       <c r="B678" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C678" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C678" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D678" s="16"/>
       <c r="E678" s="9" t="s">
@@ -13815,9 +13144,8 @@
       <c r="B679" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C679" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C679" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D679" s="16"/>
       <c r="E679" s="9" t="s">
@@ -13831,9 +13159,8 @@
       <c r="B680" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C680" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C680" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D680" s="16"/>
       <c r="E680" s="9" t="s">
@@ -13847,9 +13174,8 @@
       <c r="B681" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C681" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C681" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D681" s="16"/>
       <c r="E681" s="9" t="s">
@@ -13863,9 +13189,8 @@
       <c r="B682" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C682" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C682" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D682" s="16"/>
       <c r="E682" s="9" t="s">
@@ -13879,9 +13204,8 @@
       <c r="B683" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C683" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C683" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D683" s="16"/>
       <c r="E683" s="9" t="s">
@@ -13895,9 +13219,8 @@
       <c r="B684" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C684" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C684" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D684" s="16"/>
       <c r="E684" s="9" t="s">
@@ -13911,9 +13234,8 @@
       <c r="B685" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C685" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C685" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D685" s="16"/>
       <c r="E685" s="9" t="s">
@@ -13927,9 +13249,8 @@
       <c r="B686" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C686" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C686" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D686" s="16"/>
       <c r="E686" s="9" t="s">
@@ -13943,9 +13264,8 @@
       <c r="B687" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C687" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C687" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D687" s="16"/>
       <c r="E687" s="9" t="s">
@@ -13959,9 +13279,8 @@
       <c r="B688" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C688" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C688" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D688" s="16"/>
       <c r="E688" s="9" t="s">
@@ -13975,9 +13294,8 @@
       <c r="B689" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C689" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C689" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D689" s="16"/>
       <c r="E689" s="9" t="s">
@@ -13991,9 +13309,8 @@
       <c r="B690" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C690" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C690" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D690" s="16"/>
       <c r="E690" s="9" t="s">
@@ -14007,9 +13324,8 @@
       <c r="B691" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C691" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C691" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D691" s="16"/>
       <c r="E691" s="9" t="s">
@@ -14023,9 +13339,8 @@
       <c r="B692" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C692" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C692" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D692" s="16"/>
       <c r="E692" s="9" t="s">
@@ -14039,9 +13354,8 @@
       <c r="B693" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C693" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C693" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D693" s="16"/>
       <c r="E693" s="9" t="s">
@@ -14055,9 +13369,8 @@
       <c r="B694" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C694" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C694" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D694" s="16"/>
       <c r="E694" s="9" t="s">
@@ -14071,9 +13384,8 @@
       <c r="B695" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C695" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C695" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D695" s="16"/>
       <c r="E695" s="9" t="s">
@@ -14087,9 +13399,8 @@
       <c r="B696" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C696" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C696" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D696" s="16"/>
       <c r="E696" s="9" t="s">
@@ -14103,9 +13414,8 @@
       <c r="B697" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C697" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C697" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D697" s="16"/>
       <c r="E697" s="9" t="s">
@@ -14119,9 +13429,8 @@
       <c r="B698" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C698" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C698" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D698" s="16"/>
       <c r="E698" s="9" t="s">
@@ -14135,9 +13444,8 @@
       <c r="B699" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C699" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C699" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D699" s="16"/>
       <c r="E699" s="9" t="s">
@@ -14151,9 +13459,8 @@
       <c r="B700" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C700" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C700" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D700" s="16"/>
       <c r="E700" s="9" t="s">
@@ -14167,9 +13474,8 @@
       <c r="B701" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C701" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C701" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D701" s="16"/>
       <c r="E701" s="9" t="s">
@@ -14183,9 +13489,8 @@
       <c r="B702" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C702" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C702" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D702" s="16"/>
       <c r="E702" s="9" t="s">
@@ -14199,9 +13504,8 @@
       <c r="B703" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C703" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C703" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D703" s="16"/>
       <c r="E703" s="9" t="s">
@@ -14215,9 +13519,8 @@
       <c r="B704" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="C704" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C704" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D704" s="16"/>
       <c r="E704" s="9" t="s">
@@ -14231,9 +13534,8 @@
       <c r="B705" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C705" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C705" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D705" s="16"/>
       <c r="E705" s="9" t="s">
@@ -14247,9 +13549,8 @@
       <c r="B706" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C706" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C706" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D706" s="16"/>
       <c r="E706" s="9" t="s">
@@ -14263,9 +13564,8 @@
       <c r="B707" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C707" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C707" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D707" s="16"/>
       <c r="E707" s="9" t="s">
@@ -14279,9 +13579,8 @@
       <c r="B708" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C708" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C708" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D708" s="16"/>
       <c r="E708" s="9" t="s">
@@ -14295,9 +13594,8 @@
       <c r="B709" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C709" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C709" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D709" s="16"/>
       <c r="E709" s="9" t="s">
@@ -14311,9 +13609,8 @@
       <c r="B710" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C710" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C710" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D710" s="16"/>
       <c r="E710" s="9" t="s">
@@ -14327,9 +13624,8 @@
       <c r="B711" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C711" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C711" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D711" s="16"/>
       <c r="E711" s="9" t="s">
@@ -14343,9 +13639,8 @@
       <c r="B712" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C712" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C712" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D712" s="16"/>
       <c r="E712" s="9" t="s">
@@ -14359,9 +13654,8 @@
       <c r="B713" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="C713" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C713" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D713" s="16"/>
       <c r="E713" s="9" t="s">
@@ -14375,9 +13669,8 @@
       <c r="B714" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C714" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C714" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D714" s="16"/>
       <c r="E714" s="9" t="s">
@@ -14391,9 +13684,8 @@
       <c r="B715" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C715" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C715" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D715" s="16"/>
       <c r="E715" s="9" t="s">
@@ -14407,9 +13699,8 @@
       <c r="B716" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C716" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C716" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D716" s="16"/>
       <c r="E716" s="9" t="s">
@@ -14423,9 +13714,8 @@
       <c r="B717" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C717" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C717" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D717" s="16"/>
       <c r="E717" s="9" t="s">
@@ -14439,9 +13729,8 @@
       <c r="B718" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="C718" s="16" t="str">
-        <f>IF(ISBLANK(#REF!),"Eksternal","Internal")</f>
-        <v>Internal</v>
+      <c r="C718" s="21" t="s">
+        <v>802</v>
       </c>
       <c r="D718" s="16"/>
       <c r="E718" s="9" t="s">
@@ -14452,7 +13741,9 @@
       <c r="A719" s="20" t="s">
         <v>725</v>
       </c>
-      <c r="C719" s="21"/>
+      <c r="C719" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D719" s="19" t="s">
         <v>782</v>
       </c>
@@ -14464,7 +13755,9 @@
       <c r="A720" s="20" t="s">
         <v>727</v>
       </c>
-      <c r="C720" s="21"/>
+      <c r="C720" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D720" s="19" t="s">
         <v>782</v>
       </c>
@@ -14476,7 +13769,9 @@
       <c r="A721" s="20" t="s">
         <v>763</v>
       </c>
-      <c r="C721" s="21"/>
+      <c r="C721" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D721" s="19" t="s">
         <v>786</v>
       </c>
@@ -14488,7 +13783,9 @@
       <c r="A722" s="20" t="s">
         <v>756</v>
       </c>
-      <c r="C722" s="21"/>
+      <c r="C722" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D722" s="19" t="s">
         <v>784</v>
       </c>
@@ -14500,7 +13797,9 @@
       <c r="A723" s="20" t="s">
         <v>751</v>
       </c>
-      <c r="C723" s="21"/>
+      <c r="C723" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D723" s="19" t="s">
         <v>787</v>
       </c>
@@ -14512,7 +13811,9 @@
       <c r="A724" s="20" t="s">
         <v>741</v>
       </c>
-      <c r="C724" s="21"/>
+      <c r="C724" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D724" s="19" t="s">
         <v>781</v>
       </c>
@@ -14524,7 +13825,9 @@
       <c r="A725" s="20" t="s">
         <v>745</v>
       </c>
-      <c r="C725" s="21"/>
+      <c r="C725" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D725" s="19" t="s">
         <v>781</v>
       </c>
@@ -14536,7 +13839,9 @@
       <c r="A726" s="20" t="s">
         <v>742</v>
       </c>
-      <c r="C726" s="21"/>
+      <c r="C726" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D726" s="19" t="s">
         <v>781</v>
       </c>
@@ -14548,7 +13853,9 @@
       <c r="A727" s="20" t="s">
         <v>776</v>
       </c>
-      <c r="C727" s="21"/>
+      <c r="C727" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D727" s="19" t="s">
         <v>781</v>
       </c>
@@ -14560,7 +13867,9 @@
       <c r="A728" s="20" t="s">
         <v>757</v>
       </c>
-      <c r="C728" s="21"/>
+      <c r="C728" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D728" s="19" t="s">
         <v>784</v>
       </c>
@@ -14572,7 +13881,9 @@
       <c r="A729" s="20" t="s">
         <v>746</v>
       </c>
-      <c r="C729" s="21"/>
+      <c r="C729" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D729" s="19" t="s">
         <v>781</v>
       </c>
@@ -14584,7 +13895,9 @@
       <c r="A730" s="20" t="s">
         <v>734</v>
       </c>
-      <c r="C730" s="21"/>
+      <c r="C730" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D730" s="19" t="s">
         <v>781</v>
       </c>
@@ -14596,7 +13909,9 @@
       <c r="A731" s="20" t="s">
         <v>761</v>
       </c>
-      <c r="C731" s="21"/>
+      <c r="C731" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D731" s="19" t="s">
         <v>788</v>
       </c>
@@ -14608,7 +13923,9 @@
       <c r="A732" s="20" t="s">
         <v>762</v>
       </c>
-      <c r="C732" s="21"/>
+      <c r="C732" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D732" s="19" t="s">
         <v>784</v>
       </c>
@@ -14620,7 +13937,9 @@
       <c r="A733" s="20" t="s">
         <v>753</v>
       </c>
-      <c r="C733" s="21"/>
+      <c r="C733" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D733" s="19" t="s">
         <v>784</v>
       </c>
@@ -14632,7 +13951,9 @@
       <c r="A734" s="20" t="s">
         <v>775</v>
       </c>
-      <c r="C734" s="21"/>
+      <c r="C734" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D734" s="19" t="s">
         <v>786</v>
       </c>
@@ -14644,7 +13965,9 @@
       <c r="A735" s="20" t="s">
         <v>752</v>
       </c>
-      <c r="C735" s="21"/>
+      <c r="C735" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D735" s="19" t="s">
         <v>788</v>
       </c>
@@ -14656,7 +13979,9 @@
       <c r="A736" s="20" t="s">
         <v>771</v>
       </c>
-      <c r="C736" s="21"/>
+      <c r="C736" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D736" s="19" t="s">
         <v>781</v>
       </c>
@@ -14668,7 +13993,9 @@
       <c r="A737" s="20" t="s">
         <v>724</v>
       </c>
-      <c r="C737" s="21"/>
+      <c r="C737" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D737" s="19" t="s">
         <v>781</v>
       </c>
@@ -14680,7 +14007,9 @@
       <c r="A738" s="20" t="s">
         <v>730</v>
       </c>
-      <c r="C738" s="21"/>
+      <c r="C738" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D738" s="19" t="s">
         <v>781</v>
       </c>
@@ -14692,7 +14021,9 @@
       <c r="A739" s="20" t="s">
         <v>749</v>
       </c>
-      <c r="C739" s="21"/>
+      <c r="C739" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D739" s="19" t="s">
         <v>788</v>
       </c>
@@ -14704,7 +14035,9 @@
       <c r="A740" s="20" t="s">
         <v>755</v>
       </c>
-      <c r="C740" s="21"/>
+      <c r="C740" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D740" s="19" t="s">
         <v>784</v>
       </c>
@@ -14716,7 +14049,9 @@
       <c r="A741" s="20" t="s">
         <v>767</v>
       </c>
-      <c r="C741" s="21"/>
+      <c r="C741" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D741" s="19" t="s">
         <v>788</v>
       </c>
@@ -14728,7 +14063,9 @@
       <c r="A742" s="20" t="s">
         <v>772</v>
       </c>
-      <c r="C742" s="21"/>
+      <c r="C742" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D742" s="19" t="s">
         <v>781</v>
       </c>
@@ -14740,7 +14077,9 @@
       <c r="A743" s="20" t="s">
         <v>759</v>
       </c>
-      <c r="C743" s="21"/>
+      <c r="C743" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D743" s="19" t="s">
         <v>785</v>
       </c>
@@ -14752,7 +14091,9 @@
       <c r="A744" s="20" t="s">
         <v>765</v>
       </c>
-      <c r="C744" s="21"/>
+      <c r="C744" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D744" s="19" t="s">
         <v>784</v>
       </c>
@@ -14764,7 +14105,9 @@
       <c r="A745" s="20" t="s">
         <v>777</v>
       </c>
-      <c r="C745" s="21"/>
+      <c r="C745" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D745" s="19" t="s">
         <v>781</v>
       </c>
@@ -14776,7 +14119,9 @@
       <c r="A746" s="20" t="s">
         <v>731</v>
       </c>
-      <c r="C746" s="21"/>
+      <c r="C746" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D746" s="19" t="s">
         <v>781</v>
       </c>
@@ -14788,7 +14133,9 @@
       <c r="A747" s="20" t="s">
         <v>780</v>
       </c>
-      <c r="C747" s="21"/>
+      <c r="C747" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D747" s="19" t="s">
         <v>781</v>
       </c>
@@ -14800,7 +14147,9 @@
       <c r="A748" s="20" t="s">
         <v>748</v>
       </c>
-      <c r="C748" s="21"/>
+      <c r="C748" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D748" s="19" t="s">
         <v>781</v>
       </c>
@@ -14812,7 +14161,9 @@
       <c r="A749" s="20" t="s">
         <v>728</v>
       </c>
-      <c r="C749" s="21"/>
+      <c r="C749" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D749" s="19" t="s">
         <v>783</v>
       </c>
@@ -14824,7 +14175,9 @@
       <c r="A750" s="20" t="s">
         <v>747</v>
       </c>
-      <c r="C750" s="21"/>
+      <c r="C750" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D750" s="19" t="s">
         <v>781</v>
       </c>
@@ -14836,7 +14189,9 @@
       <c r="A751" s="20" t="s">
         <v>760</v>
       </c>
-      <c r="C751" s="21"/>
+      <c r="C751" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D751" s="19" t="s">
         <v>785</v>
       </c>
@@ -14848,7 +14203,9 @@
       <c r="A752" s="20" t="s">
         <v>737</v>
       </c>
-      <c r="C752" s="21"/>
+      <c r="C752" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D752" s="19" t="s">
         <v>781</v>
       </c>
@@ -14860,7 +14217,9 @@
       <c r="A753" s="20" t="s">
         <v>779</v>
       </c>
-      <c r="C753" s="21"/>
+      <c r="C753" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D753" s="19" t="s">
         <v>781</v>
       </c>
@@ -14872,7 +14231,9 @@
       <c r="A754" s="20" t="s">
         <v>738</v>
       </c>
-      <c r="C754" s="21"/>
+      <c r="C754" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D754" s="19" t="s">
         <v>781</v>
       </c>
@@ -14884,7 +14245,9 @@
       <c r="A755" s="20" t="s">
         <v>750</v>
       </c>
-      <c r="C755" s="21"/>
+      <c r="C755" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D755" s="19" t="s">
         <v>784</v>
       </c>
@@ -14896,7 +14259,9 @@
       <c r="A756" s="20" t="s">
         <v>732</v>
       </c>
-      <c r="C756" s="21"/>
+      <c r="C756" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D756" s="19" t="s">
         <v>781</v>
       </c>
@@ -14908,7 +14273,9 @@
       <c r="A757" s="20" t="s">
         <v>743</v>
       </c>
-      <c r="C757" s="21"/>
+      <c r="C757" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D757" s="19" t="s">
         <v>781</v>
       </c>
@@ -14920,7 +14287,9 @@
       <c r="A758" s="20" t="s">
         <v>735</v>
       </c>
-      <c r="C758" s="21"/>
+      <c r="C758" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D758" s="19" t="s">
         <v>781</v>
       </c>
@@ -14932,7 +14301,9 @@
       <c r="A759" s="20" t="s">
         <v>773</v>
       </c>
-      <c r="C759" s="21"/>
+      <c r="C759" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D759" s="19" t="s">
         <v>784</v>
       </c>
@@ -14944,7 +14315,9 @@
       <c r="A760" s="20" t="s">
         <v>768</v>
       </c>
-      <c r="C760" s="21"/>
+      <c r="C760" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D760" s="19" t="s">
         <v>784</v>
       </c>
@@ -14956,7 +14329,9 @@
       <c r="A761" s="20" t="s">
         <v>739</v>
       </c>
-      <c r="C761" s="21"/>
+      <c r="C761" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D761" s="19" t="s">
         <v>781</v>
       </c>
@@ -14968,7 +14343,9 @@
       <c r="A762" s="20" t="s">
         <v>758</v>
       </c>
-      <c r="C762" s="21"/>
+      <c r="C762" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D762" s="19" t="s">
         <v>784</v>
       </c>
@@ -14980,7 +14357,9 @@
       <c r="A763" s="20" t="s">
         <v>754</v>
       </c>
-      <c r="C763" s="21"/>
+      <c r="C763" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D763" s="19" t="s">
         <v>784</v>
       </c>
@@ -14992,7 +14371,9 @@
       <c r="A764" s="20" t="s">
         <v>770</v>
       </c>
-      <c r="C764" s="21"/>
+      <c r="C764" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D764" s="19" t="s">
         <v>788</v>
       </c>
@@ -15004,7 +14385,9 @@
       <c r="A765" s="20" t="s">
         <v>769</v>
       </c>
-      <c r="C765" s="21"/>
+      <c r="C765" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D765" s="19" t="s">
         <v>788</v>
       </c>
@@ -15016,7 +14399,9 @@
       <c r="A766" s="20" t="s">
         <v>764</v>
       </c>
-      <c r="C766" s="21"/>
+      <c r="C766" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D766" s="19" t="s">
         <v>786</v>
       </c>
@@ -15028,7 +14413,9 @@
       <c r="A767" s="20" t="s">
         <v>744</v>
       </c>
-      <c r="C767" s="21"/>
+      <c r="C767" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D767" s="19" t="s">
         <v>783</v>
       </c>
@@ -15040,7 +14427,9 @@
       <c r="A768" s="20" t="s">
         <v>774</v>
       </c>
-      <c r="C768" s="21"/>
+      <c r="C768" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D768" s="19" t="s">
         <v>786</v>
       </c>
@@ -15052,7 +14441,9 @@
       <c r="A769" s="20" t="s">
         <v>733</v>
       </c>
-      <c r="C769" s="21"/>
+      <c r="C769" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D769" s="19" t="s">
         <v>781</v>
       </c>
@@ -15064,7 +14455,9 @@
       <c r="A770" s="20" t="s">
         <v>736</v>
       </c>
-      <c r="C770" s="21"/>
+      <c r="C770" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D770" s="19" t="s">
         <v>781</v>
       </c>
@@ -15076,7 +14469,9 @@
       <c r="A771" s="20" t="s">
         <v>766</v>
       </c>
-      <c r="C771" s="21"/>
+      <c r="C771" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D771" s="19" t="s">
         <v>788</v>
       </c>
@@ -15088,7 +14483,9 @@
       <c r="A772" s="20" t="s">
         <v>740</v>
       </c>
-      <c r="C772" s="21"/>
+      <c r="C772" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D772" s="19" t="s">
         <v>781</v>
       </c>
@@ -15100,7 +14497,9 @@
       <c r="A773" s="20" t="s">
         <v>778</v>
       </c>
-      <c r="C773" s="21"/>
+      <c r="C773" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D773" s="19" t="s">
         <v>781</v>
       </c>
@@ -15112,7 +14511,9 @@
       <c r="A774" s="20" t="s">
         <v>729</v>
       </c>
-      <c r="C774" s="21"/>
+      <c r="C774" s="21" t="s">
+        <v>803</v>
+      </c>
       <c r="D774" s="19" t="s">
         <v>781</v>
       </c>
@@ -15123,6 +14524,9 @@
     <row r="775" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A775" s="20" t="s">
         <v>790</v>
+      </c>
+      <c r="C775" s="21" t="s">
+        <v>803</v>
       </c>
       <c r="D775" s="19" t="s">
         <v>781</v>
